--- a/source/bin/excel/shops.xlsx
+++ b/source/bin/excel/shops.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AB2D61-7D8C-4E13-991F-1DF2429DFA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE04409D-D456-4E8D-AD79-ACFB60559158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6565" uniqueCount="2105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6666" uniqueCount="2134">
   <si>
     <t>sheet</t>
   </si>
@@ -12387,10 +12387,6 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
-    <t>八木唯の着せ替え衣装</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
     <t>元宵の着せ替え衣装</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
@@ -12581,68 +12577,795 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
+    <t>25武侠4+4</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>自选服饰商品id</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选商品id</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>云踪侠影</t>
+  </si>
+  <si>
+    <t>雲蹤俠影</t>
+  </si>
+  <si>
+    <t>Miki Nikaidou Outfit</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲跡侠影</t>
+  </si>
+  <si>
+    <t>Shape of a Fading Echo</t>
+  </si>
+  <si>
+    <t>풍운의 그림자 협객</t>
+  </si>
+  <si>
+    <t>セレクト着せ替え</t>
+  </si>
+  <si>
+    <t>Outfit of Your Choice</t>
+  </si>
+  <si>
+    <t>선택 스킨</t>
+  </si>
+  <si>
+    <t>期間限定</t>
+  </si>
+  <si>
+    <t>Limited-Time</t>
+  </si>
+  <si>
+    <t>기간 한정</t>
+  </si>
+  <si>
+    <t>25yh4</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/bantianyinshiYH_shop.jpg</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>坂田银时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服饰</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>阪田銀時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服飾</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/guixiaotailangYH_shop.jpg</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>桂小太郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服饰</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>桂小太郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服飾</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/gaoshanjinzhuYH_shop.jpg</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高杉晋助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服饰</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高杉晉助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服飾</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/banbenchenmaYH_shop.jpg</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>坂本辰马</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服饰</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>阪本辰馬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服飾</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
     <t>投票复刻结果*4</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
-    <t>25武侠4+4</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>自选服饰商品id</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>可选商品id</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>云踪侠影</t>
-  </si>
-  <si>
-    <t>雲蹤俠影</t>
-  </si>
-  <si>
-    <t>Miki Nikaidou Outfit</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>雲跡侠影</t>
-  </si>
-  <si>
-    <t>Shape of a Fading Echo</t>
-  </si>
-  <si>
-    <t>풍운의 그림자 협객</t>
-  </si>
-  <si>
-    <t>セレクト着せ替え</t>
-  </si>
-  <si>
-    <t>Outfit of Your Choice</t>
-  </si>
-  <si>
-    <t>선택 스킨</t>
-  </si>
-  <si>
-    <t>期間限定</t>
-  </si>
-  <si>
-    <t>Limited-Time</t>
-  </si>
-  <si>
-    <t>기간 한정</t>
+    <t>麻将桌即人生</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻將桌即人生</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀卓は人生の縮図である</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>All the World's a Table</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작탁은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인생의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>축소판이다</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>坂田銀時</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の着せ替え衣装</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>桂小太郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の着せ替え衣装</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>高杉晋助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の着せ替え衣装</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>坂本辰馬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>の着せ替え衣装</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gintoki Sakata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Outfit</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kotaro Katsura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Outfit</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Shinsuke Takasugi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Outfit</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tatsuma Sakamoto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Outfit</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카츠라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코타로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타카스기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신스케</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사카모토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타츠마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사카타</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>긴토키</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨</t>
+    </r>
+    <phoneticPr fontId="31" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="87" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13242,6 +13965,26 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -13468,7 +14211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -13712,6 +14455,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -16712,7 +17461,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AB515"/>
+  <dimension ref="A1:AB522"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
@@ -21616,13 +22365,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P99">
         <v>307477</v>
       </c>
       <c r="Q99" s="19" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -50284,7 +51033,7 @@
         <v>2048</v>
       </c>
       <c r="O500" s="108" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="P500" s="15">
         <v>40011203</v>
@@ -50781,7 +51530,7 @@
         <v>563</v>
       </c>
       <c r="N507" s="51" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="O507" s="74" t="s">
         <v>1677</v>
@@ -50924,7 +51673,7 @@
         <v>563</v>
       </c>
       <c r="N509" s="113" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="O509" s="114" t="s">
         <v>1677</v>
@@ -50974,19 +51723,19 @@
         <v>2055</v>
       </c>
       <c r="F510" s="18" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G510" s="18" t="s">
         <v>2086</v>
       </c>
-      <c r="G510" s="18" t="s">
-        <v>2087</v>
-      </c>
       <c r="H510" s="103" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I510" s="103" t="s">
+        <v>2098</v>
+      </c>
+      <c r="J510" s="103" t="s">
         <v>2099</v>
-      </c>
-      <c r="I510" s="103" t="s">
-        <v>2100</v>
-      </c>
-      <c r="J510" s="103" t="s">
-        <v>2101</v>
       </c>
       <c r="K510" s="18" t="s">
         <v>2056</v>
@@ -50995,13 +51744,13 @@
         <v>2057</v>
       </c>
       <c r="M510" s="103" t="s">
+        <v>2100</v>
+      </c>
+      <c r="N510" s="103" t="s">
+        <v>2101</v>
+      </c>
+      <c r="O510" s="103" t="s">
         <v>2102</v>
-      </c>
-      <c r="N510" s="103" t="s">
-        <v>2103</v>
-      </c>
-      <c r="O510" s="103" t="s">
-        <v>2104</v>
       </c>
       <c r="P510" s="115"/>
       <c r="Q510" s="115"/>
@@ -51029,7 +51778,7 @@
     </row>
     <row r="511" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A511" s="19" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="B511">
         <v>5400</v>
@@ -51044,19 +51793,19 @@
         <v>2064</v>
       </c>
       <c r="F511" s="122" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="G511" s="103" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H511" s="102" t="s">
         <v>2094</v>
       </c>
-      <c r="H511" s="102" t="s">
+      <c r="I511" s="102" t="s">
+        <v>2095</v>
+      </c>
+      <c r="J511" s="102" t="s">
         <v>2096</v>
-      </c>
-      <c r="I511" s="102" t="s">
-        <v>2097</v>
-      </c>
-      <c r="J511" s="102" t="s">
-        <v>2098</v>
       </c>
       <c r="K511" s="19" t="s">
         <v>2068</v>
@@ -51065,13 +51814,13 @@
         <v>2071</v>
       </c>
       <c r="M511" s="19" t="s">
-        <v>2074</v>
+        <v>1462</v>
       </c>
       <c r="N511" s="50" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="O511" s="74" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="P511" s="15">
         <v>400709</v>
@@ -51115,19 +51864,19 @@
         <v>2065</v>
       </c>
       <c r="F512" s="122" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="G512" s="103" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H512" s="102" t="s">
         <v>2094</v>
       </c>
-      <c r="H512" s="102" t="s">
+      <c r="I512" s="102" t="s">
+        <v>2095</v>
+      </c>
+      <c r="J512" s="102" t="s">
         <v>2096</v>
-      </c>
-      <c r="I512" s="102" t="s">
-        <v>2097</v>
-      </c>
-      <c r="J512" s="102" t="s">
-        <v>2098</v>
       </c>
       <c r="K512" s="116" t="s">
         <v>2069</v>
@@ -51136,13 +51885,13 @@
         <v>2072</v>
       </c>
       <c r="M512" s="55" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="N512" s="55" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O512" s="118" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="P512" s="15">
         <v>40010703</v>
@@ -51186,19 +51935,19 @@
         <v>2066</v>
       </c>
       <c r="F513" s="122" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="G513" s="103" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H513" s="102" t="s">
         <v>2094</v>
       </c>
-      <c r="H513" s="102" t="s">
+      <c r="I513" s="102" t="s">
+        <v>2095</v>
+      </c>
+      <c r="J513" s="102" t="s">
         <v>2096</v>
-      </c>
-      <c r="I513" s="102" t="s">
-        <v>2097</v>
-      </c>
-      <c r="J513" s="102" t="s">
-        <v>2098</v>
       </c>
       <c r="K513" s="19" t="s">
         <v>1678</v>
@@ -51257,19 +52006,19 @@
         <v>2067</v>
       </c>
       <c r="F514" s="122" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="G514" s="103" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H514" s="102" t="s">
         <v>2094</v>
       </c>
-      <c r="H514" s="102" t="s">
+      <c r="I514" s="102" t="s">
+        <v>2095</v>
+      </c>
+      <c r="J514" s="102" t="s">
         <v>2096</v>
-      </c>
-      <c r="I514" s="102" t="s">
-        <v>2097</v>
-      </c>
-      <c r="J514" s="102" t="s">
-        <v>2098</v>
       </c>
       <c r="K514" s="117" t="s">
         <v>2070</v>
@@ -51278,13 +52027,13 @@
         <v>2073</v>
       </c>
       <c r="M514" s="117" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="N514" s="117" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="O514" s="119" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="P514" s="15">
         <v>408503</v>
@@ -51316,7 +52065,577 @@
     </row>
     <row r="515" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A515" s="19" t="s">
-        <v>2088</v>
+        <v>2116</v>
+      </c>
+      <c r="B515">
+        <v>5404</v>
+      </c>
+      <c r="C515">
+        <v>5</v>
+      </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
+      <c r="E515" s="19" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F515" s="20" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G515" s="20" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H515" s="20" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I515" s="20" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J515" s="20" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K515" t="s">
+        <v>515</v>
+      </c>
+      <c r="L515" t="s">
+        <v>516</v>
+      </c>
+      <c r="M515" t="s">
+        <v>517</v>
+      </c>
+      <c r="N515" s="50" t="s">
+        <v>1368</v>
+      </c>
+      <c r="O515" t="s">
+        <v>790</v>
+      </c>
+      <c r="P515">
+        <v>401004</v>
+      </c>
+      <c r="Q515" s="19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="R515" s="19"/>
+      <c r="S515">
+        <v>1</v>
+      </c>
+      <c r="T515">
+        <v>1</v>
+      </c>
+      <c r="U515">
+        <v>0</v>
+      </c>
+      <c r="V515" s="9">
+        <v>6</v>
+      </c>
+      <c r="W515">
+        <v>10000</v>
+      </c>
+      <c r="X515" s="9">
+        <v>250910</v>
+      </c>
+      <c r="AB515" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="516" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B516">
+        <v>5405</v>
+      </c>
+      <c r="C516">
+        <v>5</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516" s="19" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F516" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G516" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H516" s="20" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I516" s="20" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J516" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="K516" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="L516" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="M516" s="45" t="s">
+        <v>648</v>
+      </c>
+      <c r="N516" s="50" t="s">
+        <v>1381</v>
+      </c>
+      <c r="O516" s="44" t="s">
+        <v>803</v>
+      </c>
+      <c r="P516" s="9">
+        <v>403805</v>
+      </c>
+      <c r="Q516" t="s">
+        <v>928</v>
+      </c>
+      <c r="S516">
+        <v>1</v>
+      </c>
+      <c r="T516">
+        <v>1</v>
+      </c>
+      <c r="U516">
+        <v>0</v>
+      </c>
+      <c r="V516" s="9">
+        <v>7</v>
+      </c>
+      <c r="W516">
+        <v>10000</v>
+      </c>
+      <c r="X516" s="9">
+        <v>250910</v>
+      </c>
+      <c r="AB516" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="517" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B517">
+        <v>5406</v>
+      </c>
+      <c r="C517">
+        <v>5</v>
+      </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
+      <c r="E517" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F517" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G517" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H517" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I517" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J517" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K517" t="s">
+        <v>826</v>
+      </c>
+      <c r="L517" t="s">
+        <v>825</v>
+      </c>
+      <c r="M517" t="s">
+        <v>828</v>
+      </c>
+      <c r="N517" s="50" t="s">
+        <v>1334</v>
+      </c>
+      <c r="O517" t="s">
+        <v>759</v>
+      </c>
+      <c r="P517">
+        <v>400106</v>
+      </c>
+      <c r="Q517" t="s">
+        <v>1130</v>
+      </c>
+      <c r="S517">
+        <v>1</v>
+      </c>
+      <c r="T517">
+        <v>1</v>
+      </c>
+      <c r="U517">
+        <v>0</v>
+      </c>
+      <c r="V517" s="9">
+        <v>8</v>
+      </c>
+      <c r="W517">
+        <v>10000</v>
+      </c>
+      <c r="X517" s="9">
+        <v>250910</v>
+      </c>
+      <c r="AB517" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="518" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B518">
+        <v>5407</v>
+      </c>
+      <c r="C518">
+        <v>5</v>
+      </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
+      <c r="E518" s="19" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F518" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G518" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H518" s="20" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I518" s="20" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J518" s="20" t="s">
+        <v>1299</v>
+      </c>
+      <c r="K518" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="L518" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="M518" s="45" t="s">
+        <v>1302</v>
+      </c>
+      <c r="N518" s="50" t="s">
+        <v>1341</v>
+      </c>
+      <c r="O518" s="44" t="s">
+        <v>766</v>
+      </c>
+      <c r="P518" s="9">
+        <v>401204</v>
+      </c>
+      <c r="Q518" t="s">
+        <v>926</v>
+      </c>
+      <c r="S518">
+        <v>1</v>
+      </c>
+      <c r="T518">
+        <v>1</v>
+      </c>
+      <c r="U518">
+        <v>0</v>
+      </c>
+      <c r="V518" s="9">
+        <v>9</v>
+      </c>
+      <c r="W518">
+        <v>10000</v>
+      </c>
+      <c r="X518" s="9">
+        <v>250910</v>
+      </c>
+      <c r="AB518" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="519" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A519" s="19" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B519">
+        <v>5408</v>
+      </c>
+      <c r="C519">
+        <v>5</v>
+      </c>
+      <c r="D519">
+        <v>1</v>
+      </c>
+      <c r="E519" s="19" t="s">
+        <v>2104</v>
+      </c>
+      <c r="F519" s="123" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G519" s="123" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H519" s="123" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I519" s="123" t="s">
+        <v>2120</v>
+      </c>
+      <c r="J519" s="124" t="s">
+        <v>2121</v>
+      </c>
+      <c r="K519" s="19" t="s">
+        <v>2105</v>
+      </c>
+      <c r="L519" s="19" t="s">
+        <v>2106</v>
+      </c>
+      <c r="M519" s="106" t="s">
+        <v>2122</v>
+      </c>
+      <c r="N519" s="51" t="s">
+        <v>2126</v>
+      </c>
+      <c r="O519" s="88" t="s">
+        <v>2133</v>
+      </c>
+      <c r="P519" s="15">
+        <v>40011303</v>
+      </c>
+      <c r="Q519" t="s">
+        <v>926</v>
+      </c>
+      <c r="S519">
+        <v>1</v>
+      </c>
+      <c r="T519">
+        <v>1</v>
+      </c>
+      <c r="U519">
+        <v>0</v>
+      </c>
+      <c r="V519" s="9">
+        <v>1</v>
+      </c>
+      <c r="W519">
+        <v>10000</v>
+      </c>
+      <c r="X519">
+        <v>251020</v>
+      </c>
+      <c r="AB519" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="520" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B520">
+        <v>5409</v>
+      </c>
+      <c r="C520">
+        <v>5</v>
+      </c>
+      <c r="D520">
+        <v>1</v>
+      </c>
+      <c r="E520" s="19" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F520" s="123" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G520" s="123" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H520" s="123" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I520" s="123" t="s">
+        <v>2120</v>
+      </c>
+      <c r="J520" s="124" t="s">
+        <v>2121</v>
+      </c>
+      <c r="K520" s="19" t="s">
+        <v>2108</v>
+      </c>
+      <c r="L520" s="19" t="s">
+        <v>2109</v>
+      </c>
+      <c r="M520" s="106" t="s">
+        <v>2123</v>
+      </c>
+      <c r="N520" s="51" t="s">
+        <v>2127</v>
+      </c>
+      <c r="O520" s="88" t="s">
+        <v>2130</v>
+      </c>
+      <c r="P520" s="15">
+        <v>40011403</v>
+      </c>
+      <c r="Q520" t="s">
+        <v>926</v>
+      </c>
+      <c r="S520">
+        <v>1</v>
+      </c>
+      <c r="T520">
+        <v>1</v>
+      </c>
+      <c r="U520">
+        <v>0</v>
+      </c>
+      <c r="V520" s="9">
+        <v>2</v>
+      </c>
+      <c r="W520">
+        <v>10000</v>
+      </c>
+      <c r="X520">
+        <v>251020</v>
+      </c>
+      <c r="AB520" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="521" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B521">
+        <v>5410</v>
+      </c>
+      <c r="C521">
+        <v>5</v>
+      </c>
+      <c r="D521">
+        <v>1</v>
+      </c>
+      <c r="E521" s="19" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F521" s="123" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G521" s="123" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H521" s="123" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I521" s="123" t="s">
+        <v>2120</v>
+      </c>
+      <c r="J521" s="124" t="s">
+        <v>2121</v>
+      </c>
+      <c r="K521" s="19" t="s">
+        <v>2111</v>
+      </c>
+      <c r="L521" s="19" t="s">
+        <v>2112</v>
+      </c>
+      <c r="M521" s="106" t="s">
+        <v>2124</v>
+      </c>
+      <c r="N521" s="51" t="s">
+        <v>2128</v>
+      </c>
+      <c r="O521" s="88" t="s">
+        <v>2131</v>
+      </c>
+      <c r="P521" s="15">
+        <v>40011503</v>
+      </c>
+      <c r="Q521" t="s">
+        <v>926</v>
+      </c>
+      <c r="S521">
+        <v>1</v>
+      </c>
+      <c r="T521">
+        <v>1</v>
+      </c>
+      <c r="U521">
+        <v>0</v>
+      </c>
+      <c r="V521" s="9">
+        <v>3</v>
+      </c>
+      <c r="W521">
+        <v>10000</v>
+      </c>
+      <c r="X521">
+        <v>251020</v>
+      </c>
+      <c r="AB521" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="522" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B522">
+        <v>5411</v>
+      </c>
+      <c r="C522">
+        <v>5</v>
+      </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
+      <c r="E522" s="19" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F522" s="123" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G522" s="123" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H522" s="123" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I522" s="123" t="s">
+        <v>2120</v>
+      </c>
+      <c r="J522" s="124" t="s">
+        <v>2121</v>
+      </c>
+      <c r="K522" s="19" t="s">
+        <v>2114</v>
+      </c>
+      <c r="L522" s="19" t="s">
+        <v>2115</v>
+      </c>
+      <c r="M522" s="106" t="s">
+        <v>2125</v>
+      </c>
+      <c r="N522" s="51" t="s">
+        <v>2129</v>
+      </c>
+      <c r="O522" s="88" t="s">
+        <v>2132</v>
+      </c>
+      <c r="P522" s="15">
+        <v>40011603</v>
+      </c>
+      <c r="Q522" t="s">
+        <v>926</v>
+      </c>
+      <c r="S522">
+        <v>1</v>
+      </c>
+      <c r="T522">
+        <v>1</v>
+      </c>
+      <c r="U522">
+        <v>0</v>
+      </c>
+      <c r="V522" s="9">
+        <v>4</v>
+      </c>
+      <c r="W522">
+        <v>10000</v>
+      </c>
+      <c r="X522">
+        <v>251020</v>
+      </c>
+      <c r="AB522" s="9" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -51329,7 +52648,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA844279-9A7F-4CD9-96AF-9965691997B6}">
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="120" bestFit="1" customWidth="1"/>
@@ -51358,13 +52677,13 @@
         <v>30</v>
       </c>
       <c r="B2" s="120" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C2" s="120" t="s">
         <v>2090</v>
       </c>
-      <c r="C2" s="120" t="s">
-        <v>2092</v>
-      </c>
       <c r="D2" s="120" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -51424,10 +52743,10 @@
         <v>5399</v>
       </c>
       <c r="C8" s="120">
-        <v>5271</v>
+        <v>5382</v>
       </c>
       <c r="D8" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -51435,10 +52754,10 @@
         <v>5399</v>
       </c>
       <c r="C9" s="120">
-        <v>5382</v>
+        <v>5250</v>
       </c>
       <c r="D9" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -51446,7 +52765,7 @@
         <v>5399</v>
       </c>
       <c r="C10" s="120">
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="D10" s="120" t="s">
         <v>926</v>
@@ -51457,7 +52776,7 @@
         <v>5399</v>
       </c>
       <c r="C11" s="120">
-        <v>5251</v>
+        <v>5398</v>
       </c>
       <c r="D11" s="120" t="s">
         <v>926</v>
@@ -51468,7 +52787,7 @@
         <v>5399</v>
       </c>
       <c r="C12" s="120">
-        <v>5398</v>
+        <v>5396</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>926</v>
@@ -51479,7 +52798,7 @@
         <v>5399</v>
       </c>
       <c r="C13" s="120">
-        <v>5396</v>
+        <v>5021</v>
       </c>
       <c r="D13" s="120" t="s">
         <v>926</v>
@@ -51490,7 +52809,7 @@
         <v>5399</v>
       </c>
       <c r="C14" s="120">
-        <v>5021</v>
+        <v>5156</v>
       </c>
       <c r="D14" s="120" t="s">
         <v>926</v>
@@ -51501,10 +52820,10 @@
         <v>5399</v>
       </c>
       <c r="C15" s="120">
-        <v>5156</v>
+        <v>5315</v>
       </c>
       <c r="D15" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -51512,7 +52831,7 @@
         <v>5399</v>
       </c>
       <c r="C16" s="120">
-        <v>5315</v>
+        <v>5346</v>
       </c>
       <c r="D16" s="120" t="s">
         <v>928</v>
@@ -51523,10 +52842,10 @@
         <v>5399</v>
       </c>
       <c r="C17" s="120">
-        <v>5346</v>
+        <v>5022</v>
       </c>
       <c r="D17" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
@@ -51534,7 +52853,7 @@
         <v>5399</v>
       </c>
       <c r="C18" s="120">
-        <v>5022</v>
+        <v>5081</v>
       </c>
       <c r="D18" s="120" t="s">
         <v>926</v>
@@ -51545,7 +52864,7 @@
         <v>5399</v>
       </c>
       <c r="C19" s="120">
-        <v>5081</v>
+        <v>5125</v>
       </c>
       <c r="D19" s="120" t="s">
         <v>926</v>
@@ -51556,10 +52875,10 @@
         <v>5399</v>
       </c>
       <c r="C20" s="120">
-        <v>5125</v>
+        <v>5327</v>
       </c>
       <c r="D20" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
@@ -51567,10 +52886,10 @@
         <v>5399</v>
       </c>
       <c r="C21" s="120">
-        <v>5327</v>
+        <v>5348</v>
       </c>
       <c r="D21" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
@@ -51578,7 +52897,7 @@
         <v>5399</v>
       </c>
       <c r="C22" s="120">
-        <v>5348</v>
+        <v>5039</v>
       </c>
       <c r="D22" s="120" t="s">
         <v>926</v>
@@ -51589,7 +52908,7 @@
         <v>5399</v>
       </c>
       <c r="C23" s="120">
-        <v>5039</v>
+        <v>5245</v>
       </c>
       <c r="D23" s="120" t="s">
         <v>926</v>
@@ -51600,10 +52919,10 @@
         <v>5399</v>
       </c>
       <c r="C24" s="120">
-        <v>5245</v>
+        <v>5231</v>
       </c>
       <c r="D24" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
@@ -51611,7 +52930,7 @@
         <v>5399</v>
       </c>
       <c r="C25" s="120">
-        <v>5231</v>
+        <v>5361</v>
       </c>
       <c r="D25" s="120" t="s">
         <v>928</v>
@@ -51622,10 +52941,10 @@
         <v>5399</v>
       </c>
       <c r="C26" s="120">
-        <v>5361</v>
+        <v>5040</v>
       </c>
       <c r="D26" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
@@ -51633,7 +52952,7 @@
         <v>5399</v>
       </c>
       <c r="C27" s="120">
-        <v>5040</v>
+        <v>5174</v>
       </c>
       <c r="D27" s="120" t="s">
         <v>926</v>
@@ -51644,7 +52963,7 @@
         <v>5399</v>
       </c>
       <c r="C28" s="120">
-        <v>5174</v>
+        <v>5302</v>
       </c>
       <c r="D28" s="120" t="s">
         <v>926</v>
@@ -51655,7 +52974,7 @@
         <v>5399</v>
       </c>
       <c r="C29" s="120">
-        <v>5302</v>
+        <v>5388</v>
       </c>
       <c r="D29" s="120" t="s">
         <v>926</v>
@@ -51666,7 +52985,7 @@
         <v>5399</v>
       </c>
       <c r="C30" s="120">
-        <v>5388</v>
+        <v>5246</v>
       </c>
       <c r="D30" s="120" t="s">
         <v>926</v>
@@ -51677,7 +52996,7 @@
         <v>5399</v>
       </c>
       <c r="C31" s="120">
-        <v>5246</v>
+        <v>5247</v>
       </c>
       <c r="D31" s="120" t="s">
         <v>926</v>
@@ -51688,7 +53007,7 @@
         <v>5399</v>
       </c>
       <c r="C32" s="120">
-        <v>5247</v>
+        <v>5185</v>
       </c>
       <c r="D32" s="120" t="s">
         <v>926</v>
@@ -51699,10 +53018,10 @@
         <v>5399</v>
       </c>
       <c r="C33" s="120">
-        <v>5185</v>
+        <v>5293</v>
       </c>
       <c r="D33" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
@@ -51710,10 +53029,10 @@
         <v>5399</v>
       </c>
       <c r="C34" s="120">
-        <v>5293</v>
+        <v>5300</v>
       </c>
       <c r="D34" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -51721,7 +53040,7 @@
         <v>5399</v>
       </c>
       <c r="C35" s="120">
-        <v>5300</v>
+        <v>5041</v>
       </c>
       <c r="D35" s="120" t="s">
         <v>926</v>
@@ -51732,7 +53051,7 @@
         <v>5399</v>
       </c>
       <c r="C36" s="120">
-        <v>5041</v>
+        <v>5252</v>
       </c>
       <c r="D36" s="120" t="s">
         <v>926</v>
@@ -51743,7 +53062,7 @@
         <v>5399</v>
       </c>
       <c r="C37" s="120">
-        <v>5252</v>
+        <v>5204</v>
       </c>
       <c r="D37" s="120" t="s">
         <v>926</v>
@@ -51754,7 +53073,7 @@
         <v>5399</v>
       </c>
       <c r="C38" s="120">
-        <v>5204</v>
+        <v>5381</v>
       </c>
       <c r="D38" s="120" t="s">
         <v>926</v>
@@ -51765,7 +53084,7 @@
         <v>5399</v>
       </c>
       <c r="C39" s="120">
-        <v>5381</v>
+        <v>5384</v>
       </c>
       <c r="D39" s="120" t="s">
         <v>926</v>
@@ -51776,7 +53095,7 @@
         <v>5399</v>
       </c>
       <c r="C40" s="120">
-        <v>5384</v>
+        <v>5094</v>
       </c>
       <c r="D40" s="120" t="s">
         <v>926</v>
@@ -51787,7 +53106,7 @@
         <v>5399</v>
       </c>
       <c r="C41" s="120">
-        <v>5094</v>
+        <v>5082</v>
       </c>
       <c r="D41" s="120" t="s">
         <v>926</v>
@@ -51798,10 +53117,10 @@
         <v>5399</v>
       </c>
       <c r="C42" s="120">
-        <v>5082</v>
+        <v>5269</v>
       </c>
       <c r="D42" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
@@ -51809,7 +53128,7 @@
         <v>5399</v>
       </c>
       <c r="C43" s="120">
-        <v>5269</v>
+        <v>5383</v>
       </c>
       <c r="D43" s="120" t="s">
         <v>928</v>
@@ -51820,10 +53139,10 @@
         <v>5399</v>
       </c>
       <c r="C44" s="120">
-        <v>5383</v>
+        <v>5211</v>
       </c>
       <c r="D44" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
@@ -51831,7 +53150,7 @@
         <v>5399</v>
       </c>
       <c r="C45" s="120">
-        <v>5211</v>
+        <v>5242</v>
       </c>
       <c r="D45" s="120" t="s">
         <v>926</v>
@@ -51842,10 +53161,10 @@
         <v>5399</v>
       </c>
       <c r="C46" s="120">
-        <v>5275</v>
+        <v>5243</v>
       </c>
       <c r="D46" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
@@ -51853,10 +53172,10 @@
         <v>5399</v>
       </c>
       <c r="C47" s="120">
-        <v>5242</v>
+        <v>5220</v>
       </c>
       <c r="D47" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
@@ -51864,7 +53183,7 @@
         <v>5399</v>
       </c>
       <c r="C48" s="120">
-        <v>5243</v>
+        <v>5296</v>
       </c>
       <c r="D48" s="120" t="s">
         <v>926</v>
@@ -51875,10 +53194,10 @@
         <v>5399</v>
       </c>
       <c r="C49" s="120">
-        <v>5220</v>
+        <v>5339</v>
       </c>
       <c r="D49" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
@@ -51886,7 +53205,7 @@
         <v>5399</v>
       </c>
       <c r="C50" s="120">
-        <v>5296</v>
+        <v>5255</v>
       </c>
       <c r="D50" s="120" t="s">
         <v>926</v>
@@ -51897,7 +53216,7 @@
         <v>5399</v>
       </c>
       <c r="C51" s="120">
-        <v>5317</v>
+        <v>5256</v>
       </c>
       <c r="D51" s="120" t="s">
         <v>926</v>
@@ -51908,10 +53227,10 @@
         <v>5399</v>
       </c>
       <c r="C52" s="120">
-        <v>5339</v>
+        <v>5270</v>
       </c>
       <c r="D52" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
@@ -51919,7 +53238,7 @@
         <v>5399</v>
       </c>
       <c r="C53" s="120">
-        <v>5255</v>
+        <v>5326</v>
       </c>
       <c r="D53" s="120" t="s">
         <v>926</v>
@@ -51930,7 +53249,7 @@
         <v>5399</v>
       </c>
       <c r="C54" s="120">
-        <v>5256</v>
+        <v>5098</v>
       </c>
       <c r="D54" s="120" t="s">
         <v>926</v>
@@ -51941,10 +53260,10 @@
         <v>5399</v>
       </c>
       <c r="C55" s="120">
-        <v>5270</v>
+        <v>5144</v>
       </c>
       <c r="D55" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
@@ -51952,7 +53271,7 @@
         <v>5399</v>
       </c>
       <c r="C56" s="120">
-        <v>5326</v>
+        <v>5226</v>
       </c>
       <c r="D56" s="120" t="s">
         <v>926</v>
@@ -51963,7 +53282,7 @@
         <v>5399</v>
       </c>
       <c r="C57" s="120">
-        <v>5098</v>
+        <v>5360</v>
       </c>
       <c r="D57" s="120" t="s">
         <v>926</v>
@@ -51974,7 +53293,7 @@
         <v>5399</v>
       </c>
       <c r="C58" s="120">
-        <v>5144</v>
+        <v>5027</v>
       </c>
       <c r="D58" s="120" t="s">
         <v>926</v>
@@ -51985,7 +53304,7 @@
         <v>5399</v>
       </c>
       <c r="C59" s="120">
-        <v>5226</v>
+        <v>5122</v>
       </c>
       <c r="D59" s="120" t="s">
         <v>926</v>
@@ -51996,7 +53315,7 @@
         <v>5399</v>
       </c>
       <c r="C60" s="120">
-        <v>5360</v>
+        <v>5221</v>
       </c>
       <c r="D60" s="120" t="s">
         <v>926</v>
@@ -52007,7 +53326,7 @@
         <v>5399</v>
       </c>
       <c r="C61" s="120">
-        <v>5027</v>
+        <v>5301</v>
       </c>
       <c r="D61" s="120" t="s">
         <v>926</v>
@@ -52018,7 +53337,7 @@
         <v>5399</v>
       </c>
       <c r="C62" s="120">
-        <v>5122</v>
+        <v>5349</v>
       </c>
       <c r="D62" s="120" t="s">
         <v>926</v>
@@ -52029,7 +53348,7 @@
         <v>5399</v>
       </c>
       <c r="C63" s="120">
-        <v>5221</v>
+        <v>5061</v>
       </c>
       <c r="D63" s="120" t="s">
         <v>926</v>
@@ -52040,7 +53359,7 @@
         <v>5399</v>
       </c>
       <c r="C64" s="120">
-        <v>5301</v>
+        <v>5142</v>
       </c>
       <c r="D64" s="120" t="s">
         <v>926</v>
@@ -52051,7 +53370,7 @@
         <v>5399</v>
       </c>
       <c r="C65" s="120">
-        <v>5349</v>
+        <v>5290</v>
       </c>
       <c r="D65" s="120" t="s">
         <v>926</v>
@@ -52062,10 +53381,10 @@
         <v>5399</v>
       </c>
       <c r="C66" s="120">
-        <v>5061</v>
+        <v>5335</v>
       </c>
       <c r="D66" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.2">
@@ -52073,7 +53392,7 @@
         <v>5399</v>
       </c>
       <c r="C67" s="120">
-        <v>5142</v>
+        <v>5083</v>
       </c>
       <c r="D67" s="120" t="s">
         <v>926</v>
@@ -52084,7 +53403,7 @@
         <v>5399</v>
       </c>
       <c r="C68" s="120">
-        <v>5290</v>
+        <v>5291</v>
       </c>
       <c r="D68" s="120" t="s">
         <v>926</v>
@@ -52095,10 +53414,10 @@
         <v>5399</v>
       </c>
       <c r="C69" s="120">
-        <v>5335</v>
+        <v>5337</v>
       </c>
       <c r="D69" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.2">
@@ -52106,7 +53425,7 @@
         <v>5399</v>
       </c>
       <c r="C70" s="120">
-        <v>5083</v>
+        <v>5126</v>
       </c>
       <c r="D70" s="120" t="s">
         <v>926</v>
@@ -52117,7 +53436,7 @@
         <v>5399</v>
       </c>
       <c r="C71" s="120">
-        <v>5291</v>
+        <v>5150</v>
       </c>
       <c r="D71" s="120" t="s">
         <v>926</v>
@@ -52128,7 +53447,7 @@
         <v>5399</v>
       </c>
       <c r="C72" s="120">
-        <v>5337</v>
+        <v>5205</v>
       </c>
       <c r="D72" s="120" t="s">
         <v>926</v>
@@ -52139,10 +53458,10 @@
         <v>5399</v>
       </c>
       <c r="C73" s="120">
-        <v>5126</v>
+        <v>5386</v>
       </c>
       <c r="D73" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.2">
@@ -52150,10 +53469,10 @@
         <v>5399</v>
       </c>
       <c r="C74" s="120">
-        <v>5150</v>
+        <v>5376</v>
       </c>
       <c r="D74" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.2">
@@ -52161,7 +53480,7 @@
         <v>5399</v>
       </c>
       <c r="C75" s="120">
-        <v>5205</v>
+        <v>5084</v>
       </c>
       <c r="D75" s="120" t="s">
         <v>926</v>
@@ -52172,10 +53491,10 @@
         <v>5399</v>
       </c>
       <c r="C76" s="120">
-        <v>5386</v>
+        <v>5121</v>
       </c>
       <c r="D76" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.2">
@@ -52183,7 +53502,7 @@
         <v>5399</v>
       </c>
       <c r="C77" s="120">
-        <v>5376</v>
+        <v>5262</v>
       </c>
       <c r="D77" s="120" t="s">
         <v>928</v>
@@ -52194,7 +53513,7 @@
         <v>5399</v>
       </c>
       <c r="C78" s="120">
-        <v>5084</v>
+        <v>5387</v>
       </c>
       <c r="D78" s="120" t="s">
         <v>926</v>
@@ -52205,7 +53524,7 @@
         <v>5399</v>
       </c>
       <c r="C79" s="120">
-        <v>5121</v>
+        <v>5133</v>
       </c>
       <c r="D79" s="120" t="s">
         <v>926</v>
@@ -52216,7 +53535,7 @@
         <v>5399</v>
       </c>
       <c r="C80" s="120">
-        <v>5262</v>
+        <v>5151</v>
       </c>
       <c r="D80" s="120" t="s">
         <v>928</v>
@@ -52227,7 +53546,7 @@
         <v>5399</v>
       </c>
       <c r="C81" s="120">
-        <v>5387</v>
+        <v>5351</v>
       </c>
       <c r="D81" s="120" t="s">
         <v>926</v>
@@ -52238,10 +53557,10 @@
         <v>5399</v>
       </c>
       <c r="C82" s="120">
-        <v>5133</v>
+        <v>5370</v>
       </c>
       <c r="D82" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.2">
@@ -52249,10 +53568,10 @@
         <v>5399</v>
       </c>
       <c r="C83" s="120">
-        <v>5151</v>
+        <v>5241</v>
       </c>
       <c r="D83" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.2">
@@ -52260,7 +53579,7 @@
         <v>5399</v>
       </c>
       <c r="C84" s="120">
-        <v>5351</v>
+        <v>5249</v>
       </c>
       <c r="D84" s="120" t="s">
         <v>926</v>
@@ -52271,10 +53590,10 @@
         <v>5399</v>
       </c>
       <c r="C85" s="120">
-        <v>5370</v>
+        <v>5344</v>
       </c>
       <c r="D85" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.2">
@@ -52282,7 +53601,7 @@
         <v>5399</v>
       </c>
       <c r="C86" s="120">
-        <v>5241</v>
+        <v>5240</v>
       </c>
       <c r="D86" s="120" t="s">
         <v>926</v>
@@ -52293,7 +53612,7 @@
         <v>5399</v>
       </c>
       <c r="C87" s="120">
-        <v>5249</v>
+        <v>5186</v>
       </c>
       <c r="D87" s="120" t="s">
         <v>926</v>
@@ -52304,7 +53623,7 @@
         <v>5399</v>
       </c>
       <c r="C88" s="120">
-        <v>5344</v>
+        <v>5308</v>
       </c>
       <c r="D88" s="120" t="s">
         <v>926</v>
@@ -52315,10 +53634,10 @@
         <v>5399</v>
       </c>
       <c r="C89" s="120">
-        <v>5240</v>
+        <v>5380</v>
       </c>
       <c r="D89" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.2">
@@ -52326,10 +53645,10 @@
         <v>5399</v>
       </c>
       <c r="C90" s="120">
-        <v>5186</v>
+        <v>5358</v>
       </c>
       <c r="D90" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.2">
@@ -52337,7 +53656,7 @@
         <v>5399</v>
       </c>
       <c r="C91" s="120">
-        <v>5308</v>
+        <v>5143</v>
       </c>
       <c r="D91" s="120" t="s">
         <v>926</v>
@@ -52348,10 +53667,10 @@
         <v>5399</v>
       </c>
       <c r="C92" s="120">
-        <v>5380</v>
+        <v>5330</v>
       </c>
       <c r="D92" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.2">
@@ -52359,10 +53678,10 @@
         <v>5399</v>
       </c>
       <c r="C93" s="120">
-        <v>5358</v>
+        <v>5110</v>
       </c>
       <c r="D93" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.2">
@@ -52370,7 +53689,7 @@
         <v>5399</v>
       </c>
       <c r="C94" s="120">
-        <v>5143</v>
+        <v>5198</v>
       </c>
       <c r="D94" s="120" t="s">
         <v>926</v>
@@ -52381,7 +53700,7 @@
         <v>5399</v>
       </c>
       <c r="C95" s="120">
-        <v>5330</v>
+        <v>5338</v>
       </c>
       <c r="D95" s="120" t="s">
         <v>926</v>
@@ -52392,10 +53711,10 @@
         <v>5399</v>
       </c>
       <c r="C96" s="120">
-        <v>5110</v>
+        <v>5391</v>
       </c>
       <c r="D96" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.2">
@@ -52403,7 +53722,7 @@
         <v>5399</v>
       </c>
       <c r="C97" s="120">
-        <v>5198</v>
+        <v>5248</v>
       </c>
       <c r="D97" s="120" t="s">
         <v>926</v>
@@ -52414,10 +53733,10 @@
         <v>5399</v>
       </c>
       <c r="C98" s="120">
-        <v>5338</v>
+        <v>5232</v>
       </c>
       <c r="D98" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.2">
@@ -52425,10 +53744,10 @@
         <v>5399</v>
       </c>
       <c r="C99" s="120">
-        <v>5391</v>
+        <v>5363</v>
       </c>
       <c r="D99" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.2">
@@ -52436,7 +53755,7 @@
         <v>5399</v>
       </c>
       <c r="C100" s="120">
-        <v>5248</v>
+        <v>5253</v>
       </c>
       <c r="D100" s="120" t="s">
         <v>926</v>
@@ -52447,10 +53766,10 @@
         <v>5399</v>
       </c>
       <c r="C101" s="120">
-        <v>5232</v>
+        <v>5210</v>
       </c>
       <c r="D101" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.2">
@@ -52458,7 +53777,7 @@
         <v>5399</v>
       </c>
       <c r="C102" s="120">
-        <v>5363</v>
+        <v>5362</v>
       </c>
       <c r="D102" s="120" t="s">
         <v>926</v>
@@ -52469,7 +53788,7 @@
         <v>5399</v>
       </c>
       <c r="C103" s="120">
-        <v>5253</v>
+        <v>5385</v>
       </c>
       <c r="D103" s="120" t="s">
         <v>926</v>
@@ -52480,7 +53799,7 @@
         <v>5399</v>
       </c>
       <c r="C104" s="120">
-        <v>5210</v>
+        <v>5239</v>
       </c>
       <c r="D104" s="120" t="s">
         <v>926</v>
@@ -52491,10 +53810,10 @@
         <v>5399</v>
       </c>
       <c r="C105" s="120">
-        <v>5362</v>
+        <v>5213</v>
       </c>
       <c r="D105" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.2">
@@ -52502,7 +53821,7 @@
         <v>5399</v>
       </c>
       <c r="C106" s="120">
-        <v>5385</v>
+        <v>5281</v>
       </c>
       <c r="D106" s="120" t="s">
         <v>926</v>
@@ -52513,7 +53832,7 @@
         <v>5399</v>
       </c>
       <c r="C107" s="120">
-        <v>5239</v>
+        <v>5353</v>
       </c>
       <c r="D107" s="120" t="s">
         <v>926</v>
@@ -52524,10 +53843,10 @@
         <v>5399</v>
       </c>
       <c r="C108" s="120">
-        <v>5213</v>
+        <v>5157</v>
       </c>
       <c r="D108" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.2">
@@ -52535,10 +53854,10 @@
         <v>5399</v>
       </c>
       <c r="C109" s="120">
-        <v>5281</v>
+        <v>5342</v>
       </c>
       <c r="D109" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.2">
@@ -52546,7 +53865,7 @@
         <v>5399</v>
       </c>
       <c r="C110" s="120">
-        <v>5353</v>
+        <v>5254</v>
       </c>
       <c r="D110" s="120" t="s">
         <v>926</v>
@@ -52557,7 +53876,7 @@
         <v>5399</v>
       </c>
       <c r="C111" s="120">
-        <v>5157</v>
+        <v>5316</v>
       </c>
       <c r="D111" s="120" t="s">
         <v>926</v>
@@ -52568,10 +53887,10 @@
         <v>5399</v>
       </c>
       <c r="C112" s="120">
-        <v>5342</v>
+        <v>5134</v>
       </c>
       <c r="D112" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.2">
@@ -52579,10 +53898,10 @@
         <v>5399</v>
       </c>
       <c r="C113" s="120">
-        <v>5254</v>
+        <v>5182</v>
       </c>
       <c r="D113" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.2">
@@ -52590,7 +53909,7 @@
         <v>5399</v>
       </c>
       <c r="C114" s="120">
-        <v>5316</v>
+        <v>5329</v>
       </c>
       <c r="D114" s="120" t="s">
         <v>926</v>
@@ -52601,10 +53920,10 @@
         <v>5399</v>
       </c>
       <c r="C115" s="120">
-        <v>5134</v>
+        <v>5379</v>
       </c>
       <c r="D115" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.2">
@@ -52612,10 +53931,10 @@
         <v>5399</v>
       </c>
       <c r="C116" s="120">
-        <v>5182</v>
+        <v>5225</v>
       </c>
       <c r="D116" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.2">
@@ -52623,10 +53942,10 @@
         <v>5399</v>
       </c>
       <c r="C117" s="120">
-        <v>5329</v>
+        <v>5395</v>
       </c>
       <c r="D117" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.2">
@@ -52634,10 +53953,10 @@
         <v>5399</v>
       </c>
       <c r="C118" s="120">
-        <v>5379</v>
+        <v>5189</v>
       </c>
       <c r="D118" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.2">
@@ -52645,7 +53964,7 @@
         <v>5399</v>
       </c>
       <c r="C119" s="120">
-        <v>5225</v>
+        <v>5264</v>
       </c>
       <c r="D119" s="120" t="s">
         <v>926</v>
@@ -52656,10 +53975,10 @@
         <v>5399</v>
       </c>
       <c r="C120" s="120">
-        <v>5395</v>
+        <v>5222</v>
       </c>
       <c r="D120" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.2">
@@ -52667,7 +53986,7 @@
         <v>5399</v>
       </c>
       <c r="C121" s="120">
-        <v>5189</v>
+        <v>5303</v>
       </c>
       <c r="D121" s="120" t="s">
         <v>926</v>
@@ -52678,7 +53997,7 @@
         <v>5399</v>
       </c>
       <c r="C122" s="120">
-        <v>5264</v>
+        <v>5176</v>
       </c>
       <c r="D122" s="120" t="s">
         <v>926</v>
@@ -52689,10 +54008,10 @@
         <v>5399</v>
       </c>
       <c r="C123" s="120">
-        <v>5314</v>
+        <v>5309</v>
       </c>
       <c r="D123" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.2">
@@ -52700,7 +54019,7 @@
         <v>5399</v>
       </c>
       <c r="C124" s="120">
-        <v>5222</v>
+        <v>5340</v>
       </c>
       <c r="D124" s="120" t="s">
         <v>926</v>
@@ -52711,10 +54030,10 @@
         <v>5399</v>
       </c>
       <c r="C125" s="120">
-        <v>5303</v>
+        <v>5214</v>
       </c>
       <c r="D125" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.2">
@@ -52722,7 +54041,7 @@
         <v>5399</v>
       </c>
       <c r="C126" s="120">
-        <v>5176</v>
+        <v>5199</v>
       </c>
       <c r="D126" s="120" t="s">
         <v>926</v>
@@ -52733,10 +54052,10 @@
         <v>5399</v>
       </c>
       <c r="C127" s="120">
-        <v>5309</v>
+        <v>5324</v>
       </c>
       <c r="D127" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.2">
@@ -52744,10 +54063,10 @@
         <v>5399</v>
       </c>
       <c r="C128" s="120">
-        <v>5340</v>
+        <v>5263</v>
       </c>
       <c r="D128" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.2">
@@ -52755,10 +54074,10 @@
         <v>5399</v>
       </c>
       <c r="C129" s="120">
-        <v>5214</v>
+        <v>5373</v>
       </c>
       <c r="D129" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.2">
@@ -52766,7 +54085,7 @@
         <v>5399</v>
       </c>
       <c r="C130" s="120">
-        <v>5199</v>
+        <v>5265</v>
       </c>
       <c r="D130" s="120" t="s">
         <v>926</v>
@@ -52777,7 +54096,7 @@
         <v>5399</v>
       </c>
       <c r="C131" s="120">
-        <v>5324</v>
+        <v>5328</v>
       </c>
       <c r="D131" s="120" t="s">
         <v>928</v>
@@ -52788,7 +54107,7 @@
         <v>5399</v>
       </c>
       <c r="C132" s="120">
-        <v>5263</v>
+        <v>5295</v>
       </c>
       <c r="D132" s="120" t="s">
         <v>928</v>
@@ -52799,7 +54118,7 @@
         <v>5399</v>
       </c>
       <c r="C133" s="120">
-        <v>5373</v>
+        <v>5276</v>
       </c>
       <c r="D133" s="120" t="s">
         <v>926</v>
@@ -52810,10 +54129,10 @@
         <v>5399</v>
       </c>
       <c r="C134" s="120">
-        <v>5265</v>
+        <v>5323</v>
       </c>
       <c r="D134" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.2">
@@ -52821,10 +54140,10 @@
         <v>5399</v>
       </c>
       <c r="C135" s="120">
-        <v>5328</v>
+        <v>5282</v>
       </c>
       <c r="D135" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.2">
@@ -52832,10 +54151,10 @@
         <v>5399</v>
       </c>
       <c r="C136" s="120">
-        <v>5295</v>
+        <v>5352</v>
       </c>
       <c r="D136" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.2">
@@ -52843,7 +54162,7 @@
         <v>5399</v>
       </c>
       <c r="C137" s="120">
-        <v>5276</v>
+        <v>5364</v>
       </c>
       <c r="D137" s="120" t="s">
         <v>926</v>
@@ -52854,10 +54173,10 @@
         <v>5399</v>
       </c>
       <c r="C138" s="120">
-        <v>5323</v>
+        <v>5393</v>
       </c>
       <c r="D138" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.2">
@@ -52865,7 +54184,7 @@
         <v>5399</v>
       </c>
       <c r="C139" s="120">
-        <v>5282</v>
+        <v>5190</v>
       </c>
       <c r="D139" s="120" t="s">
         <v>926</v>
@@ -52876,7 +54195,7 @@
         <v>5399</v>
       </c>
       <c r="C140" s="120">
-        <v>5352</v>
+        <v>5357</v>
       </c>
       <c r="D140" s="120" t="s">
         <v>926</v>
@@ -52887,7 +54206,7 @@
         <v>5399</v>
       </c>
       <c r="C141" s="120">
-        <v>5364</v>
+        <v>5378</v>
       </c>
       <c r="D141" s="120" t="s">
         <v>926</v>
@@ -52898,7 +54217,7 @@
         <v>5399</v>
       </c>
       <c r="C142" s="120">
-        <v>5393</v>
+        <v>5307</v>
       </c>
       <c r="D142" s="120" t="s">
         <v>926</v>
@@ -52909,7 +54228,7 @@
         <v>5399</v>
       </c>
       <c r="C143" s="120">
-        <v>5190</v>
+        <v>5345</v>
       </c>
       <c r="D143" s="120" t="s">
         <v>926</v>
@@ -52920,10 +54239,10 @@
         <v>5399</v>
       </c>
       <c r="C144" s="120">
-        <v>5357</v>
+        <v>5394</v>
       </c>
       <c r="D144" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.2">
@@ -52931,10 +54250,10 @@
         <v>5399</v>
       </c>
       <c r="C145" s="120">
-        <v>5378</v>
+        <v>5371</v>
       </c>
       <c r="D145" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.2">
@@ -52942,7 +54261,7 @@
         <v>5399</v>
       </c>
       <c r="C146" s="120">
-        <v>5307</v>
+        <v>5365</v>
       </c>
       <c r="D146" s="120" t="s">
         <v>926</v>
@@ -52953,10 +54272,10 @@
         <v>5399</v>
       </c>
       <c r="C147" s="120">
-        <v>5345</v>
+        <v>5347</v>
       </c>
       <c r="D147" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.2">
@@ -52964,10 +54283,10 @@
         <v>5399</v>
       </c>
       <c r="C148" s="120">
-        <v>5394</v>
+        <v>5292</v>
       </c>
       <c r="D148" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.2">
@@ -52975,10 +54294,10 @@
         <v>5399</v>
       </c>
       <c r="C149" s="120">
-        <v>5371</v>
+        <v>5343</v>
       </c>
       <c r="D149" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.2">
@@ -52986,7 +54305,7 @@
         <v>5399</v>
       </c>
       <c r="C150" s="120">
-        <v>5365</v>
+        <v>5374</v>
       </c>
       <c r="D150" s="120" t="s">
         <v>926</v>
@@ -52997,7 +54316,7 @@
         <v>5399</v>
       </c>
       <c r="C151" s="120">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="D151" s="120" t="s">
         <v>928</v>
@@ -53008,10 +54327,10 @@
         <v>5399</v>
       </c>
       <c r="C152" s="120">
-        <v>5292</v>
+        <v>5390</v>
       </c>
       <c r="D152" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.2">
@@ -53019,10 +54338,10 @@
         <v>5399</v>
       </c>
       <c r="C153" s="120">
-        <v>5343</v>
+        <v>5341</v>
       </c>
       <c r="D153" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.2">
@@ -53030,10 +54349,10 @@
         <v>5399</v>
       </c>
       <c r="C154" s="120">
-        <v>5374</v>
+        <v>5336</v>
       </c>
       <c r="D154" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.2">
@@ -53041,10 +54360,10 @@
         <v>5399</v>
       </c>
       <c r="C155" s="120">
-        <v>5350</v>
+        <v>5356</v>
       </c>
       <c r="D155" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.2">
@@ -53052,10 +54371,10 @@
         <v>5399</v>
       </c>
       <c r="C156" s="120">
-        <v>5390</v>
+        <v>5372</v>
       </c>
       <c r="D156" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.2">
@@ -53063,10 +54382,10 @@
         <v>5399</v>
       </c>
       <c r="C157" s="120">
-        <v>5341</v>
+        <v>5325</v>
       </c>
       <c r="D157" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.2">
@@ -53074,10 +54393,10 @@
         <v>5399</v>
       </c>
       <c r="C158" s="120">
-        <v>5336</v>
+        <v>5397</v>
       </c>
       <c r="D158" s="120" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.2">
@@ -53085,7 +54404,7 @@
         <v>5399</v>
       </c>
       <c r="C159" s="120">
-        <v>5356</v>
+        <v>5355</v>
       </c>
       <c r="D159" s="120" t="s">
         <v>926</v>
@@ -53096,7 +54415,7 @@
         <v>5399</v>
       </c>
       <c r="C160" s="120">
-        <v>5372</v>
+        <v>5377</v>
       </c>
       <c r="D160" s="120" t="s">
         <v>926</v>
@@ -53107,10 +54426,10 @@
         <v>5399</v>
       </c>
       <c r="C161" s="120">
-        <v>5325</v>
+        <v>5392</v>
       </c>
       <c r="D161" s="120" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.2">
@@ -53118,7 +54437,7 @@
         <v>5399</v>
       </c>
       <c r="C162" s="120">
-        <v>5397</v>
+        <v>5375</v>
       </c>
       <c r="D162" s="120" t="s">
         <v>926</v>
@@ -53129,7 +54448,7 @@
         <v>5399</v>
       </c>
       <c r="C163" s="120">
-        <v>5355</v>
+        <v>5354</v>
       </c>
       <c r="D163" s="120" t="s">
         <v>926</v>
@@ -53140,53 +54459,9 @@
         <v>5399</v>
       </c>
       <c r="C164" s="120">
-        <v>5377</v>
+        <v>5359</v>
       </c>
       <c r="D164" s="120" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B165" s="121">
-        <v>5399</v>
-      </c>
-      <c r="C165" s="120">
-        <v>5392</v>
-      </c>
-      <c r="D165" s="120" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B166" s="121">
-        <v>5399</v>
-      </c>
-      <c r="C166" s="120">
-        <v>5375</v>
-      </c>
-      <c r="D166" s="120" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B167" s="121">
-        <v>5399</v>
-      </c>
-      <c r="C167" s="120">
-        <v>5354</v>
-      </c>
-      <c r="D167" s="120" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B168" s="121">
-        <v>5399</v>
-      </c>
-      <c r="C168" s="120">
-        <v>5359</v>
-      </c>
-      <c r="D168" s="120" t="s">
         <v>926</v>
       </c>
     </row>

--- a/source/bin/excel/shops.xlsx
+++ b/source/bin/excel/shops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68192CF7-07DD-42D9-A203-6A9990471441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E13B32-E4FC-4087-9D9C-261EF88DA929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="2029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7165" uniqueCount="2035">
   <si>
     <t>sheet</t>
   </si>
@@ -6207,6 +6207,30 @@
   </si>
   <si>
     <t>Spring Celebration</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbd</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>25dj4</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/tongren_dj_shop.jpg</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/yasina_dj_shop.jpg</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/shinai_dj_shop.jpg</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>extendRes/skin_shop/lifa_dj_shop.jpg</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -10063,7 +10087,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AB561"/>
+  <dimension ref="A1:AB565"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
@@ -47407,7 +47431,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="561" spans="2:28" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:28" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B561">
         <v>5443</v>
       </c>
@@ -47475,6 +47499,293 @@
         <v>260210</v>
       </c>
       <c r="AB561" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="562" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A562" s="19" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B562">
+        <v>5444</v>
+      </c>
+      <c r="C562">
+        <v>5</v>
+      </c>
+      <c r="D562">
+        <v>1</v>
+      </c>
+      <c r="E562" s="19" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="I562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="J562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="K562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="M562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="O562" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="P562" s="15">
+        <v>40012203</v>
+      </c>
+      <c r="Q562" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S562">
+        <v>1</v>
+      </c>
+      <c r="T562">
+        <v>1</v>
+      </c>
+      <c r="U562">
+        <v>0</v>
+      </c>
+      <c r="V562" s="9">
+        <v>1</v>
+      </c>
+      <c r="W562">
+        <v>10000</v>
+      </c>
+      <c r="X562">
+        <v>260410</v>
+      </c>
+      <c r="AB562" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="563" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B563">
+        <v>5445</v>
+      </c>
+      <c r="C563">
+        <v>5</v>
+      </c>
+      <c r="D563">
+        <v>1</v>
+      </c>
+      <c r="E563" s="19" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="I563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="J563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="K563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="M563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="O563" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="P563" s="15">
+        <v>40012303</v>
+      </c>
+      <c r="Q563" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S563">
+        <v>1</v>
+      </c>
+      <c r="T563">
+        <v>1</v>
+      </c>
+      <c r="U563">
+        <v>0</v>
+      </c>
+      <c r="V563" s="9">
+        <v>2</v>
+      </c>
+      <c r="W563">
+        <v>10000</v>
+      </c>
+      <c r="X563">
+        <v>260410</v>
+      </c>
+      <c r="AB563" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="564" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B564">
+        <v>5446</v>
+      </c>
+      <c r="C564">
+        <v>5</v>
+      </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
+      <c r="E564" s="19" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="I564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="J564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="K564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="M564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="O564" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="P564" s="15">
+        <v>40012403</v>
+      </c>
+      <c r="Q564" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S564">
+        <v>1</v>
+      </c>
+      <c r="T564">
+        <v>1</v>
+      </c>
+      <c r="U564">
+        <v>0</v>
+      </c>
+      <c r="V564" s="9">
+        <v>3</v>
+      </c>
+      <c r="W564">
+        <v>10000</v>
+      </c>
+      <c r="X564">
+        <v>260410</v>
+      </c>
+      <c r="AB564" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="565" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B565">
+        <v>5447</v>
+      </c>
+      <c r="C565">
+        <v>5</v>
+      </c>
+      <c r="D565">
+        <v>1</v>
+      </c>
+      <c r="E565" s="19" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="I565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="J565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="K565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="L565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="M565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="O565" s="123" t="s">
+        <v>2029</v>
+      </c>
+      <c r="P565" s="15">
+        <v>40012503</v>
+      </c>
+      <c r="Q565" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S565">
+        <v>1</v>
+      </c>
+      <c r="T565">
+        <v>1</v>
+      </c>
+      <c r="U565">
+        <v>0</v>
+      </c>
+      <c r="V565" s="9">
+        <v>4</v>
+      </c>
+      <c r="W565">
+        <v>10000</v>
+      </c>
+      <c r="X565">
+        <v>260410</v>
+      </c>
+      <c r="AB565" s="9" t="s">
         <v>234</v>
       </c>
     </row>

--- a/source/bin/excel/shops.xlsx
+++ b/source/bin/excel/shops.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF98517-C217-49ED-A910-9F225E39D6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674CA634-0ED9-4A32-9A53-5D74F2DD8AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7680" uniqueCount="2120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7753" uniqueCount="2122">
   <si>
     <t>sheet</t>
   </si>
@@ -6736,6 +6736,14 @@
   </si>
   <si>
     <t>302009-8</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>2607投票结果6</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>一姬当千</t>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
@@ -10642,7 +10650,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AC592"/>
+  <dimension ref="A1:AC598"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
@@ -50197,6 +50205,435 @@
         <v>234</v>
       </c>
     </row>
+    <row r="593" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A593" s="19" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B593">
+        <v>5482</v>
+      </c>
+      <c r="C593">
+        <v>5</v>
+      </c>
+      <c r="D593">
+        <v>1</v>
+      </c>
+      <c r="E593" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F593" s="19" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G593" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H593" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I593" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J593" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K593" t="s">
+        <v>794</v>
+      </c>
+      <c r="L593" t="s">
+        <v>795</v>
+      </c>
+      <c r="M593" t="s">
+        <v>704</v>
+      </c>
+      <c r="N593" s="50" t="s">
+        <v>705</v>
+      </c>
+      <c r="O593" t="s">
+        <v>706</v>
+      </c>
+      <c r="P593">
+        <v>400105</v>
+      </c>
+      <c r="Q593" t="s">
+        <v>737</v>
+      </c>
+      <c r="S593">
+        <v>1</v>
+      </c>
+      <c r="T593">
+        <v>1</v>
+      </c>
+      <c r="U593">
+        <v>0</v>
+      </c>
+      <c r="V593" s="9">
+        <v>9</v>
+      </c>
+      <c r="W593">
+        <v>10000</v>
+      </c>
+      <c r="X593">
+        <v>260710</v>
+      </c>
+      <c r="AB593" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="594" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B594">
+        <v>5483</v>
+      </c>
+      <c r="C594">
+        <v>5</v>
+      </c>
+      <c r="D594">
+        <v>1</v>
+      </c>
+      <c r="E594" s="19" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F594" s="25" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G594" s="25" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H594" s="20" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I594" s="20" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J594" s="25" t="s">
+        <v>1308</v>
+      </c>
+      <c r="K594" t="s">
+        <v>855</v>
+      </c>
+      <c r="L594" t="s">
+        <v>856</v>
+      </c>
+      <c r="M594" t="s">
+        <v>857</v>
+      </c>
+      <c r="N594" s="50" t="s">
+        <v>858</v>
+      </c>
+      <c r="O594" t="s">
+        <v>859</v>
+      </c>
+      <c r="P594">
+        <v>402905</v>
+      </c>
+      <c r="Q594" t="s">
+        <v>737</v>
+      </c>
+      <c r="S594">
+        <v>1</v>
+      </c>
+      <c r="T594">
+        <v>1</v>
+      </c>
+      <c r="U594">
+        <v>0</v>
+      </c>
+      <c r="V594" s="9">
+        <v>10</v>
+      </c>
+      <c r="W594">
+        <v>10000</v>
+      </c>
+      <c r="X594">
+        <v>260710</v>
+      </c>
+      <c r="AB594" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="595" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B595">
+        <v>5484</v>
+      </c>
+      <c r="C595">
+        <v>5</v>
+      </c>
+      <c r="D595">
+        <v>1</v>
+      </c>
+      <c r="E595" s="19" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F595" s="60" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G595" s="61" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H595" s="55" t="s">
+        <v>1488</v>
+      </c>
+      <c r="I595" s="55" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J595" s="55" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K595" s="19" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L595" s="19" t="s">
+        <v>1492</v>
+      </c>
+      <c r="M595" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="N595" s="51" t="s">
+        <v>1494</v>
+      </c>
+      <c r="O595" s="19" t="s">
+        <v>1495</v>
+      </c>
+      <c r="P595" s="10">
+        <v>406703</v>
+      </c>
+      <c r="Q595" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S595">
+        <v>1</v>
+      </c>
+      <c r="T595">
+        <v>1</v>
+      </c>
+      <c r="U595">
+        <v>0</v>
+      </c>
+      <c r="V595" s="9">
+        <v>11</v>
+      </c>
+      <c r="W595">
+        <v>10000</v>
+      </c>
+      <c r="X595">
+        <v>260710</v>
+      </c>
+      <c r="AB595" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="596" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B596">
+        <v>5485</v>
+      </c>
+      <c r="C596">
+        <v>5</v>
+      </c>
+      <c r="D596">
+        <v>1</v>
+      </c>
+      <c r="E596" s="19" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F596" s="70" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G596" s="70" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H596" s="82" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I596" s="82" t="s">
+        <v>1693</v>
+      </c>
+      <c r="J596" s="82" t="s">
+        <v>1694</v>
+      </c>
+      <c r="K596" s="19" t="s">
+        <v>751</v>
+      </c>
+      <c r="L596" t="s">
+        <v>752</v>
+      </c>
+      <c r="M596" s="19" t="s">
+        <v>753</v>
+      </c>
+      <c r="N596" s="50" t="s">
+        <v>754</v>
+      </c>
+      <c r="O596" t="s">
+        <v>755</v>
+      </c>
+      <c r="P596" s="71">
+        <v>401205</v>
+      </c>
+      <c r="Q596" t="s">
+        <v>737</v>
+      </c>
+      <c r="S596">
+        <v>1</v>
+      </c>
+      <c r="T596">
+        <v>1</v>
+      </c>
+      <c r="U596">
+        <v>0</v>
+      </c>
+      <c r="V596" s="9">
+        <v>12</v>
+      </c>
+      <c r="W596">
+        <v>10000</v>
+      </c>
+      <c r="X596">
+        <v>260710</v>
+      </c>
+      <c r="AB596" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="597" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B597">
+        <v>5486</v>
+      </c>
+      <c r="C597">
+        <v>5</v>
+      </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
+      <c r="E597" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F597" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G597" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H597" t="s">
+        <v>1410</v>
+      </c>
+      <c r="I597" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J597" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K597" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L597" t="s">
+        <v>1285</v>
+      </c>
+      <c r="M597" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N597" t="s">
+        <v>1287</v>
+      </c>
+      <c r="O597" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P597">
+        <v>404704</v>
+      </c>
+      <c r="Q597" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S597">
+        <v>1</v>
+      </c>
+      <c r="T597">
+        <v>1</v>
+      </c>
+      <c r="U597">
+        <v>0</v>
+      </c>
+      <c r="V597" s="9">
+        <v>13</v>
+      </c>
+      <c r="W597">
+        <v>10000</v>
+      </c>
+      <c r="X597">
+        <v>260710</v>
+      </c>
+      <c r="AB597" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="598" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B598">
+        <v>5487</v>
+      </c>
+      <c r="C598">
+        <v>5</v>
+      </c>
+      <c r="D598">
+        <v>1</v>
+      </c>
+      <c r="E598" s="19" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F598" s="61" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G598" s="61" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H598" s="55" t="s">
+        <v>1647</v>
+      </c>
+      <c r="I598" s="55" t="s">
+        <v>1648</v>
+      </c>
+      <c r="J598" s="66" t="s">
+        <v>1649</v>
+      </c>
+      <c r="K598" s="19" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L598" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M598" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N598" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="O598" s="74" t="s">
+        <v>1044</v>
+      </c>
+      <c r="P598" s="71">
+        <v>404505</v>
+      </c>
+      <c r="Q598" s="19" t="s">
+        <v>1032</v>
+      </c>
+      <c r="S598">
+        <v>1</v>
+      </c>
+      <c r="T598">
+        <v>1</v>
+      </c>
+      <c r="U598">
+        <v>0</v>
+      </c>
+      <c r="V598" s="9">
+        <v>14</v>
+      </c>
+      <c r="W598">
+        <v>10000</v>
+      </c>
+      <c r="X598">
+        <v>260710</v>
+      </c>
+      <c r="AB598" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50207,7 +50644,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D350"/>
+  <dimension ref="A1:D344"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="120" bestFit="1" customWidth="1"/>
@@ -52058,7 +52495,7 @@
         <v>5465</v>
       </c>
       <c r="C167" s="120">
-        <v>5212</v>
+        <v>5250</v>
       </c>
       <c r="D167" s="120" t="s">
         <v>737</v>
@@ -52069,7 +52506,7 @@
         <v>5465</v>
       </c>
       <c r="C168" s="120">
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="D168" s="120" t="s">
         <v>737</v>
@@ -52080,7 +52517,7 @@
         <v>5465</v>
       </c>
       <c r="C169" s="120">
-        <v>5251</v>
+        <v>5398</v>
       </c>
       <c r="D169" s="120" t="s">
         <v>737</v>
@@ -52091,7 +52528,7 @@
         <v>5465</v>
       </c>
       <c r="C170" s="120">
-        <v>5398</v>
+        <v>5396</v>
       </c>
       <c r="D170" s="120" t="s">
         <v>737</v>
@@ -52102,7 +52539,7 @@
         <v>5465</v>
       </c>
       <c r="C171" s="120">
-        <v>5396</v>
+        <v>5021</v>
       </c>
       <c r="D171" s="120" t="s">
         <v>737</v>
@@ -52113,7 +52550,7 @@
         <v>5465</v>
       </c>
       <c r="C172" s="120">
-        <v>5021</v>
+        <v>5156</v>
       </c>
       <c r="D172" s="120" t="s">
         <v>737</v>
@@ -52124,10 +52561,10 @@
         <v>5465</v>
       </c>
       <c r="C173" s="120">
-        <v>5156</v>
+        <v>5315</v>
       </c>
       <c r="D173" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
@@ -52135,7 +52572,7 @@
         <v>5465</v>
       </c>
       <c r="C174" s="120">
-        <v>5315</v>
+        <v>5346</v>
       </c>
       <c r="D174" s="120" t="s">
         <v>1032</v>
@@ -52146,10 +52583,10 @@
         <v>5465</v>
       </c>
       <c r="C175" s="120">
-        <v>5346</v>
+        <v>5022</v>
       </c>
       <c r="D175" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
@@ -52157,7 +52594,7 @@
         <v>5465</v>
       </c>
       <c r="C176" s="120">
-        <v>5022</v>
+        <v>5081</v>
       </c>
       <c r="D176" s="120" t="s">
         <v>737</v>
@@ -52168,7 +52605,7 @@
         <v>5465</v>
       </c>
       <c r="C177" s="120">
-        <v>5081</v>
+        <v>5125</v>
       </c>
       <c r="D177" s="120" t="s">
         <v>737</v>
@@ -52179,10 +52616,10 @@
         <v>5465</v>
       </c>
       <c r="C178" s="120">
-        <v>5125</v>
+        <v>5327</v>
       </c>
       <c r="D178" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.2">
@@ -52190,10 +52627,10 @@
         <v>5465</v>
       </c>
       <c r="C179" s="120">
-        <v>5327</v>
+        <v>5348</v>
       </c>
       <c r="D179" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.2">
@@ -52201,7 +52638,7 @@
         <v>5465</v>
       </c>
       <c r="C180" s="120">
-        <v>5348</v>
+        <v>5039</v>
       </c>
       <c r="D180" s="120" t="s">
         <v>737</v>
@@ -52212,7 +52649,7 @@
         <v>5465</v>
       </c>
       <c r="C181" s="120">
-        <v>5039</v>
+        <v>5245</v>
       </c>
       <c r="D181" s="120" t="s">
         <v>737</v>
@@ -52223,10 +52660,10 @@
         <v>5465</v>
       </c>
       <c r="C182" s="120">
-        <v>5245</v>
+        <v>5231</v>
       </c>
       <c r="D182" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.2">
@@ -52234,7 +52671,7 @@
         <v>5465</v>
       </c>
       <c r="C183" s="120">
-        <v>5231</v>
+        <v>5361</v>
       </c>
       <c r="D183" s="120" t="s">
         <v>1032</v>
@@ -52245,10 +52682,10 @@
         <v>5465</v>
       </c>
       <c r="C184" s="120">
-        <v>5361</v>
+        <v>5040</v>
       </c>
       <c r="D184" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.2">
@@ -52256,7 +52693,7 @@
         <v>5465</v>
       </c>
       <c r="C185" s="120">
-        <v>5040</v>
+        <v>5174</v>
       </c>
       <c r="D185" s="120" t="s">
         <v>737</v>
@@ -52267,7 +52704,7 @@
         <v>5465</v>
       </c>
       <c r="C186" s="120">
-        <v>5174</v>
+        <v>5302</v>
       </c>
       <c r="D186" s="120" t="s">
         <v>737</v>
@@ -52278,7 +52715,7 @@
         <v>5465</v>
       </c>
       <c r="C187" s="120">
-        <v>5302</v>
+        <v>5388</v>
       </c>
       <c r="D187" s="120" t="s">
         <v>737</v>
@@ -52289,7 +52726,7 @@
         <v>5465</v>
       </c>
       <c r="C188" s="120">
-        <v>5388</v>
+        <v>5246</v>
       </c>
       <c r="D188" s="120" t="s">
         <v>737</v>
@@ -52300,7 +52737,7 @@
         <v>5465</v>
       </c>
       <c r="C189" s="120">
-        <v>5246</v>
+        <v>5247</v>
       </c>
       <c r="D189" s="120" t="s">
         <v>737</v>
@@ -52311,7 +52748,7 @@
         <v>5465</v>
       </c>
       <c r="C190" s="120">
-        <v>5247</v>
+        <v>5185</v>
       </c>
       <c r="D190" s="120" t="s">
         <v>737</v>
@@ -52322,10 +52759,10 @@
         <v>5465</v>
       </c>
       <c r="C191" s="120">
-        <v>5185</v>
+        <v>5293</v>
       </c>
       <c r="D191" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.2">
@@ -52333,10 +52770,10 @@
         <v>5465</v>
       </c>
       <c r="C192" s="120">
-        <v>5293</v>
+        <v>5300</v>
       </c>
       <c r="D192" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.2">
@@ -52344,7 +52781,7 @@
         <v>5465</v>
       </c>
       <c r="C193" s="120">
-        <v>5300</v>
+        <v>5041</v>
       </c>
       <c r="D193" s="120" t="s">
         <v>737</v>
@@ -52355,7 +52792,7 @@
         <v>5465</v>
       </c>
       <c r="C194" s="120">
-        <v>5041</v>
+        <v>5252</v>
       </c>
       <c r="D194" s="120" t="s">
         <v>737</v>
@@ -52366,7 +52803,7 @@
         <v>5465</v>
       </c>
       <c r="C195" s="120">
-        <v>5252</v>
+        <v>5204</v>
       </c>
       <c r="D195" s="120" t="s">
         <v>737</v>
@@ -52377,7 +52814,7 @@
         <v>5465</v>
       </c>
       <c r="C196" s="120">
-        <v>5204</v>
+        <v>5381</v>
       </c>
       <c r="D196" s="120" t="s">
         <v>737</v>
@@ -52388,7 +52825,7 @@
         <v>5465</v>
       </c>
       <c r="C197" s="120">
-        <v>5381</v>
+        <v>5094</v>
       </c>
       <c r="D197" s="120" t="s">
         <v>737</v>
@@ -52399,7 +52836,7 @@
         <v>5465</v>
       </c>
       <c r="C198" s="120">
-        <v>5094</v>
+        <v>5082</v>
       </c>
       <c r="D198" s="120" t="s">
         <v>737</v>
@@ -52410,10 +52847,10 @@
         <v>5465</v>
       </c>
       <c r="C199" s="120">
-        <v>5082</v>
+        <v>5269</v>
       </c>
       <c r="D199" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.2">
@@ -52421,10 +52858,10 @@
         <v>5465</v>
       </c>
       <c r="C200" s="120">
-        <v>5269</v>
+        <v>5211</v>
       </c>
       <c r="D200" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.2">
@@ -52432,7 +52869,7 @@
         <v>5465</v>
       </c>
       <c r="C201" s="120">
-        <v>5211</v>
+        <v>5242</v>
       </c>
       <c r="D201" s="120" t="s">
         <v>737</v>
@@ -52443,7 +52880,7 @@
         <v>5465</v>
       </c>
       <c r="C202" s="120">
-        <v>5242</v>
+        <v>5243</v>
       </c>
       <c r="D202" s="120" t="s">
         <v>737</v>
@@ -52454,10 +52891,10 @@
         <v>5465</v>
       </c>
       <c r="C203" s="120">
-        <v>5243</v>
+        <v>5220</v>
       </c>
       <c r="D203" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.2">
@@ -52465,10 +52902,10 @@
         <v>5465</v>
       </c>
       <c r="C204" s="120">
-        <v>5220</v>
+        <v>5296</v>
       </c>
       <c r="D204" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.2">
@@ -52476,7 +52913,7 @@
         <v>5465</v>
       </c>
       <c r="C205" s="120">
-        <v>5296</v>
+        <v>5255</v>
       </c>
       <c r="D205" s="120" t="s">
         <v>737</v>
@@ -52487,7 +52924,7 @@
         <v>5465</v>
       </c>
       <c r="C206" s="120">
-        <v>5339</v>
+        <v>5256</v>
       </c>
       <c r="D206" s="120" t="s">
         <v>737</v>
@@ -52498,10 +52935,10 @@
         <v>5465</v>
       </c>
       <c r="C207" s="120">
-        <v>5255</v>
+        <v>5270</v>
       </c>
       <c r="D207" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="208" spans="2:4" x14ac:dyDescent="0.2">
@@ -52509,7 +52946,7 @@
         <v>5465</v>
       </c>
       <c r="C208" s="120">
-        <v>5256</v>
+        <v>5326</v>
       </c>
       <c r="D208" s="120" t="s">
         <v>737</v>
@@ -52520,10 +52957,10 @@
         <v>5465</v>
       </c>
       <c r="C209" s="120">
-        <v>5270</v>
+        <v>5098</v>
       </c>
       <c r="D209" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="210" spans="2:4" x14ac:dyDescent="0.2">
@@ -52531,7 +52968,7 @@
         <v>5465</v>
       </c>
       <c r="C210" s="120">
-        <v>5326</v>
+        <v>5144</v>
       </c>
       <c r="D210" s="120" t="s">
         <v>737</v>
@@ -52542,7 +52979,7 @@
         <v>5465</v>
       </c>
       <c r="C211" s="120">
-        <v>5098</v>
+        <v>5226</v>
       </c>
       <c r="D211" s="120" t="s">
         <v>737</v>
@@ -52553,7 +52990,7 @@
         <v>5465</v>
       </c>
       <c r="C212" s="120">
-        <v>5144</v>
+        <v>5360</v>
       </c>
       <c r="D212" s="120" t="s">
         <v>737</v>
@@ -52564,7 +53001,7 @@
         <v>5465</v>
       </c>
       <c r="C213" s="120">
-        <v>5226</v>
+        <v>5027</v>
       </c>
       <c r="D213" s="120" t="s">
         <v>737</v>
@@ -52575,7 +53012,7 @@
         <v>5465</v>
       </c>
       <c r="C214" s="120">
-        <v>5360</v>
+        <v>5122</v>
       </c>
       <c r="D214" s="120" t="s">
         <v>737</v>
@@ -52586,7 +53023,7 @@
         <v>5465</v>
       </c>
       <c r="C215" s="120">
-        <v>5027</v>
+        <v>5221</v>
       </c>
       <c r="D215" s="120" t="s">
         <v>737</v>
@@ -52597,7 +53034,7 @@
         <v>5465</v>
       </c>
       <c r="C216" s="120">
-        <v>5122</v>
+        <v>5301</v>
       </c>
       <c r="D216" s="120" t="s">
         <v>737</v>
@@ -52608,7 +53045,7 @@
         <v>5465</v>
       </c>
       <c r="C217" s="120">
-        <v>5221</v>
+        <v>5349</v>
       </c>
       <c r="D217" s="120" t="s">
         <v>737</v>
@@ -52619,7 +53056,7 @@
         <v>5465</v>
       </c>
       <c r="C218" s="120">
-        <v>5301</v>
+        <v>5061</v>
       </c>
       <c r="D218" s="120" t="s">
         <v>737</v>
@@ -52630,7 +53067,7 @@
         <v>5465</v>
       </c>
       <c r="C219" s="120">
-        <v>5349</v>
+        <v>5142</v>
       </c>
       <c r="D219" s="120" t="s">
         <v>737</v>
@@ -52641,7 +53078,7 @@
         <v>5465</v>
       </c>
       <c r="C220" s="120">
-        <v>5061</v>
+        <v>5290</v>
       </c>
       <c r="D220" s="120" t="s">
         <v>737</v>
@@ -52652,10 +53089,10 @@
         <v>5465</v>
       </c>
       <c r="C221" s="120">
-        <v>5142</v>
+        <v>5335</v>
       </c>
       <c r="D221" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="222" spans="2:4" x14ac:dyDescent="0.2">
@@ -52663,7 +53100,7 @@
         <v>5465</v>
       </c>
       <c r="C222" s="120">
-        <v>5290</v>
+        <v>5083</v>
       </c>
       <c r="D222" s="120" t="s">
         <v>737</v>
@@ -52674,10 +53111,10 @@
         <v>5465</v>
       </c>
       <c r="C223" s="120">
-        <v>5335</v>
+        <v>5291</v>
       </c>
       <c r="D223" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="224" spans="2:4" x14ac:dyDescent="0.2">
@@ -52685,7 +53122,7 @@
         <v>5465</v>
       </c>
       <c r="C224" s="120">
-        <v>5083</v>
+        <v>5337</v>
       </c>
       <c r="D224" s="120" t="s">
         <v>737</v>
@@ -52696,7 +53133,7 @@
         <v>5465</v>
       </c>
       <c r="C225" s="120">
-        <v>5291</v>
+        <v>5126</v>
       </c>
       <c r="D225" s="120" t="s">
         <v>737</v>
@@ -52707,7 +53144,7 @@
         <v>5465</v>
       </c>
       <c r="C226" s="120">
-        <v>5337</v>
+        <v>5150</v>
       </c>
       <c r="D226" s="120" t="s">
         <v>737</v>
@@ -52718,7 +53155,7 @@
         <v>5465</v>
       </c>
       <c r="C227" s="120">
-        <v>5126</v>
+        <v>5205</v>
       </c>
       <c r="D227" s="120" t="s">
         <v>737</v>
@@ -52729,10 +53166,10 @@
         <v>5465</v>
       </c>
       <c r="C228" s="120">
-        <v>5150</v>
+        <v>5386</v>
       </c>
       <c r="D228" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="229" spans="2:4" x14ac:dyDescent="0.2">
@@ -52740,10 +53177,10 @@
         <v>5465</v>
       </c>
       <c r="C229" s="120">
-        <v>5205</v>
+        <v>5376</v>
       </c>
       <c r="D229" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="230" spans="2:4" x14ac:dyDescent="0.2">
@@ -52751,10 +53188,10 @@
         <v>5465</v>
       </c>
       <c r="C230" s="120">
-        <v>5386</v>
+        <v>5084</v>
       </c>
       <c r="D230" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="231" spans="2:4" x14ac:dyDescent="0.2">
@@ -52762,10 +53199,10 @@
         <v>5465</v>
       </c>
       <c r="C231" s="120">
-        <v>5376</v>
+        <v>5121</v>
       </c>
       <c r="D231" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="232" spans="2:4" x14ac:dyDescent="0.2">
@@ -52773,10 +53210,10 @@
         <v>5465</v>
       </c>
       <c r="C232" s="120">
-        <v>5084</v>
+        <v>5262</v>
       </c>
       <c r="D232" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="233" spans="2:4" x14ac:dyDescent="0.2">
@@ -52784,7 +53221,7 @@
         <v>5465</v>
       </c>
       <c r="C233" s="120">
-        <v>5121</v>
+        <v>5387</v>
       </c>
       <c r="D233" s="120" t="s">
         <v>737</v>
@@ -52795,10 +53232,10 @@
         <v>5465</v>
       </c>
       <c r="C234" s="120">
-        <v>5262</v>
+        <v>5133</v>
       </c>
       <c r="D234" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="235" spans="2:4" x14ac:dyDescent="0.2">
@@ -52806,10 +53243,10 @@
         <v>5465</v>
       </c>
       <c r="C235" s="120">
-        <v>5387</v>
+        <v>5151</v>
       </c>
       <c r="D235" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="236" spans="2:4" x14ac:dyDescent="0.2">
@@ -52817,7 +53254,7 @@
         <v>5465</v>
       </c>
       <c r="C236" s="120">
-        <v>5133</v>
+        <v>5351</v>
       </c>
       <c r="D236" s="120" t="s">
         <v>737</v>
@@ -52828,7 +53265,7 @@
         <v>5465</v>
       </c>
       <c r="C237" s="120">
-        <v>5151</v>
+        <v>5370</v>
       </c>
       <c r="D237" s="120" t="s">
         <v>1032</v>
@@ -52839,7 +53276,7 @@
         <v>5465</v>
       </c>
       <c r="C238" s="120">
-        <v>5351</v>
+        <v>5241</v>
       </c>
       <c r="D238" s="120" t="s">
         <v>737</v>
@@ -52850,10 +53287,10 @@
         <v>5465</v>
       </c>
       <c r="C239" s="120">
-        <v>5370</v>
+        <v>5249</v>
       </c>
       <c r="D239" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="240" spans="2:4" x14ac:dyDescent="0.2">
@@ -52861,7 +53298,7 @@
         <v>5465</v>
       </c>
       <c r="C240" s="120">
-        <v>5241</v>
+        <v>5344</v>
       </c>
       <c r="D240" s="120" t="s">
         <v>737</v>
@@ -52872,7 +53309,7 @@
         <v>5465</v>
       </c>
       <c r="C241" s="120">
-        <v>5249</v>
+        <v>5240</v>
       </c>
       <c r="D241" s="120" t="s">
         <v>737</v>
@@ -52883,7 +53320,7 @@
         <v>5465</v>
       </c>
       <c r="C242" s="120">
-        <v>5344</v>
+        <v>5186</v>
       </c>
       <c r="D242" s="120" t="s">
         <v>737</v>
@@ -52894,7 +53331,7 @@
         <v>5465</v>
       </c>
       <c r="C243" s="120">
-        <v>5240</v>
+        <v>5308</v>
       </c>
       <c r="D243" s="120" t="s">
         <v>737</v>
@@ -52905,10 +53342,10 @@
         <v>5465</v>
       </c>
       <c r="C244" s="120">
-        <v>5186</v>
+        <v>5380</v>
       </c>
       <c r="D244" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="245" spans="2:4" x14ac:dyDescent="0.2">
@@ -52916,10 +53353,10 @@
         <v>5465</v>
       </c>
       <c r="C245" s="120">
-        <v>5308</v>
+        <v>5358</v>
       </c>
       <c r="D245" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="246" spans="2:4" x14ac:dyDescent="0.2">
@@ -52927,10 +53364,10 @@
         <v>5465</v>
       </c>
       <c r="C246" s="120">
-        <v>5380</v>
+        <v>5143</v>
       </c>
       <c r="D246" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="247" spans="2:4" x14ac:dyDescent="0.2">
@@ -52938,10 +53375,10 @@
         <v>5465</v>
       </c>
       <c r="C247" s="120">
-        <v>5358</v>
+        <v>5330</v>
       </c>
       <c r="D247" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="248" spans="2:4" x14ac:dyDescent="0.2">
@@ -52949,7 +53386,7 @@
         <v>5465</v>
       </c>
       <c r="C248" s="120">
-        <v>5143</v>
+        <v>5110</v>
       </c>
       <c r="D248" s="120" t="s">
         <v>737</v>
@@ -52960,7 +53397,7 @@
         <v>5465</v>
       </c>
       <c r="C249" s="120">
-        <v>5330</v>
+        <v>5198</v>
       </c>
       <c r="D249" s="120" t="s">
         <v>737</v>
@@ -52971,7 +53408,7 @@
         <v>5465</v>
       </c>
       <c r="C250" s="120">
-        <v>5110</v>
+        <v>5338</v>
       </c>
       <c r="D250" s="120" t="s">
         <v>737</v>
@@ -52982,10 +53419,10 @@
         <v>5465</v>
       </c>
       <c r="C251" s="120">
-        <v>5198</v>
+        <v>5391</v>
       </c>
       <c r="D251" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="252" spans="2:4" x14ac:dyDescent="0.2">
@@ -52993,7 +53430,7 @@
         <v>5465</v>
       </c>
       <c r="C252" s="120">
-        <v>5338</v>
+        <v>5248</v>
       </c>
       <c r="D252" s="120" t="s">
         <v>737</v>
@@ -53004,7 +53441,7 @@
         <v>5465</v>
       </c>
       <c r="C253" s="120">
-        <v>5391</v>
+        <v>5232</v>
       </c>
       <c r="D253" s="120" t="s">
         <v>1032</v>
@@ -53015,7 +53452,7 @@
         <v>5465</v>
       </c>
       <c r="C254" s="120">
-        <v>5248</v>
+        <v>5363</v>
       </c>
       <c r="D254" s="120" t="s">
         <v>737</v>
@@ -53026,10 +53463,10 @@
         <v>5465</v>
       </c>
       <c r="C255" s="120">
-        <v>5232</v>
+        <v>5253</v>
       </c>
       <c r="D255" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="256" spans="2:4" x14ac:dyDescent="0.2">
@@ -53037,7 +53474,7 @@
         <v>5465</v>
       </c>
       <c r="C256" s="120">
-        <v>5363</v>
+        <v>5210</v>
       </c>
       <c r="D256" s="120" t="s">
         <v>737</v>
@@ -53048,7 +53485,7 @@
         <v>5465</v>
       </c>
       <c r="C257" s="120">
-        <v>5253</v>
+        <v>5362</v>
       </c>
       <c r="D257" s="120" t="s">
         <v>737</v>
@@ -53059,7 +53496,7 @@
         <v>5465</v>
       </c>
       <c r="C258" s="120">
-        <v>5210</v>
+        <v>5239</v>
       </c>
       <c r="D258" s="120" t="s">
         <v>737</v>
@@ -53070,10 +53507,10 @@
         <v>5465</v>
       </c>
       <c r="C259" s="120">
-        <v>5362</v>
+        <v>5213</v>
       </c>
       <c r="D259" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="260" spans="2:4" x14ac:dyDescent="0.2">
@@ -53081,7 +53518,7 @@
         <v>5465</v>
       </c>
       <c r="C260" s="120">
-        <v>5239</v>
+        <v>5353</v>
       </c>
       <c r="D260" s="120" t="s">
         <v>737</v>
@@ -53092,10 +53529,10 @@
         <v>5465</v>
       </c>
       <c r="C261" s="120">
-        <v>5213</v>
+        <v>5157</v>
       </c>
       <c r="D261" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="262" spans="2:4" x14ac:dyDescent="0.2">
@@ -53103,10 +53540,10 @@
         <v>5465</v>
       </c>
       <c r="C262" s="120">
-        <v>5281</v>
+        <v>5342</v>
       </c>
       <c r="D262" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="263" spans="2:4" x14ac:dyDescent="0.2">
@@ -53114,7 +53551,7 @@
         <v>5465</v>
       </c>
       <c r="C263" s="120">
-        <v>5353</v>
+        <v>5254</v>
       </c>
       <c r="D263" s="120" t="s">
         <v>737</v>
@@ -53125,7 +53562,7 @@
         <v>5465</v>
       </c>
       <c r="C264" s="120">
-        <v>5157</v>
+        <v>5316</v>
       </c>
       <c r="D264" s="120" t="s">
         <v>737</v>
@@ -53136,10 +53573,10 @@
         <v>5465</v>
       </c>
       <c r="C265" s="120">
-        <v>5342</v>
+        <v>5134</v>
       </c>
       <c r="D265" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="266" spans="2:4" x14ac:dyDescent="0.2">
@@ -53147,10 +53584,10 @@
         <v>5465</v>
       </c>
       <c r="C266" s="120">
-        <v>5254</v>
+        <v>5182</v>
       </c>
       <c r="D266" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="267" spans="2:4" x14ac:dyDescent="0.2">
@@ -53158,7 +53595,7 @@
         <v>5465</v>
       </c>
       <c r="C267" s="120">
-        <v>5316</v>
+        <v>5329</v>
       </c>
       <c r="D267" s="120" t="s">
         <v>737</v>
@@ -53169,10 +53606,10 @@
         <v>5465</v>
       </c>
       <c r="C268" s="120">
-        <v>5134</v>
+        <v>5379</v>
       </c>
       <c r="D268" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="269" spans="2:4" x14ac:dyDescent="0.2">
@@ -53180,10 +53617,10 @@
         <v>5465</v>
       </c>
       <c r="C269" s="120">
-        <v>5182</v>
+        <v>5225</v>
       </c>
       <c r="D269" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="270" spans="2:4" x14ac:dyDescent="0.2">
@@ -53191,10 +53628,10 @@
         <v>5465</v>
       </c>
       <c r="C270" s="120">
-        <v>5329</v>
+        <v>5395</v>
       </c>
       <c r="D270" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="271" spans="2:4" x14ac:dyDescent="0.2">
@@ -53202,10 +53639,10 @@
         <v>5465</v>
       </c>
       <c r="C271" s="120">
-        <v>5379</v>
+        <v>5189</v>
       </c>
       <c r="D271" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="272" spans="2:4" x14ac:dyDescent="0.2">
@@ -53213,7 +53650,7 @@
         <v>5465</v>
       </c>
       <c r="C272" s="120">
-        <v>5225</v>
+        <v>5264</v>
       </c>
       <c r="D272" s="120" t="s">
         <v>737</v>
@@ -53224,10 +53661,10 @@
         <v>5465</v>
       </c>
       <c r="C273" s="120">
-        <v>5395</v>
+        <v>5222</v>
       </c>
       <c r="D273" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="274" spans="2:4" x14ac:dyDescent="0.2">
@@ -53235,7 +53672,7 @@
         <v>5465</v>
       </c>
       <c r="C274" s="120">
-        <v>5189</v>
+        <v>5303</v>
       </c>
       <c r="D274" s="120" t="s">
         <v>737</v>
@@ -53246,7 +53683,7 @@
         <v>5465</v>
       </c>
       <c r="C275" s="120">
-        <v>5264</v>
+        <v>5176</v>
       </c>
       <c r="D275" s="120" t="s">
         <v>737</v>
@@ -53257,7 +53694,7 @@
         <v>5465</v>
       </c>
       <c r="C276" s="120">
-        <v>5222</v>
+        <v>5309</v>
       </c>
       <c r="D276" s="120" t="s">
         <v>737</v>
@@ -53268,7 +53705,7 @@
         <v>5465</v>
       </c>
       <c r="C277" s="120">
-        <v>5303</v>
+        <v>5340</v>
       </c>
       <c r="D277" s="120" t="s">
         <v>737</v>
@@ -53279,10 +53716,10 @@
         <v>5465</v>
       </c>
       <c r="C278" s="120">
-        <v>5176</v>
+        <v>5214</v>
       </c>
       <c r="D278" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="279" spans="2:4" x14ac:dyDescent="0.2">
@@ -53290,7 +53727,7 @@
         <v>5465</v>
       </c>
       <c r="C279" s="120">
-        <v>5309</v>
+        <v>5199</v>
       </c>
       <c r="D279" s="120" t="s">
         <v>737</v>
@@ -53301,10 +53738,10 @@
         <v>5465</v>
       </c>
       <c r="C280" s="120">
-        <v>5340</v>
+        <v>5263</v>
       </c>
       <c r="D280" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="281" spans="2:4" x14ac:dyDescent="0.2">
@@ -53312,10 +53749,10 @@
         <v>5465</v>
       </c>
       <c r="C281" s="120">
-        <v>5214</v>
+        <v>5373</v>
       </c>
       <c r="D281" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="282" spans="2:4" x14ac:dyDescent="0.2">
@@ -53323,7 +53760,7 @@
         <v>5465</v>
       </c>
       <c r="C282" s="120">
-        <v>5199</v>
+        <v>5265</v>
       </c>
       <c r="D282" s="120" t="s">
         <v>737</v>
@@ -53334,7 +53771,7 @@
         <v>5465</v>
       </c>
       <c r="C283" s="120">
-        <v>5324</v>
+        <v>5295</v>
       </c>
       <c r="D283" s="120" t="s">
         <v>1032</v>
@@ -53345,10 +53782,10 @@
         <v>5465</v>
       </c>
       <c r="C284" s="120">
-        <v>5263</v>
+        <v>5276</v>
       </c>
       <c r="D284" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="285" spans="2:4" x14ac:dyDescent="0.2">
@@ -53356,10 +53793,10 @@
         <v>5465</v>
       </c>
       <c r="C285" s="120">
-        <v>5373</v>
+        <v>5323</v>
       </c>
       <c r="D285" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="286" spans="2:4" x14ac:dyDescent="0.2">
@@ -53367,7 +53804,7 @@
         <v>5465</v>
       </c>
       <c r="C286" s="120">
-        <v>5265</v>
+        <v>5282</v>
       </c>
       <c r="D286" s="120" t="s">
         <v>737</v>
@@ -53378,10 +53815,10 @@
         <v>5465</v>
       </c>
       <c r="C287" s="120">
-        <v>5328</v>
+        <v>5352</v>
       </c>
       <c r="D287" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="288" spans="2:4" x14ac:dyDescent="0.2">
@@ -53389,10 +53826,10 @@
         <v>5465</v>
       </c>
       <c r="C288" s="120">
-        <v>5295</v>
+        <v>5364</v>
       </c>
       <c r="D288" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="289" spans="2:4" x14ac:dyDescent="0.2">
@@ -53400,7 +53837,7 @@
         <v>5465</v>
       </c>
       <c r="C289" s="120">
-        <v>5276</v>
+        <v>5393</v>
       </c>
       <c r="D289" s="120" t="s">
         <v>737</v>
@@ -53411,10 +53848,10 @@
         <v>5465</v>
       </c>
       <c r="C290" s="120">
-        <v>5323</v>
+        <v>5190</v>
       </c>
       <c r="D290" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="291" spans="2:4" x14ac:dyDescent="0.2">
@@ -53422,7 +53859,7 @@
         <v>5465</v>
       </c>
       <c r="C291" s="120">
-        <v>5282</v>
+        <v>5357</v>
       </c>
       <c r="D291" s="120" t="s">
         <v>737</v>
@@ -53433,7 +53870,7 @@
         <v>5465</v>
       </c>
       <c r="C292" s="120">
-        <v>5352</v>
+        <v>5378</v>
       </c>
       <c r="D292" s="120" t="s">
         <v>737</v>
@@ -53444,7 +53881,7 @@
         <v>5465</v>
       </c>
       <c r="C293" s="120">
-        <v>5364</v>
+        <v>5307</v>
       </c>
       <c r="D293" s="120" t="s">
         <v>737</v>
@@ -53455,7 +53892,7 @@
         <v>5465</v>
       </c>
       <c r="C294" s="120">
-        <v>5393</v>
+        <v>5345</v>
       </c>
       <c r="D294" s="120" t="s">
         <v>737</v>
@@ -53466,10 +53903,10 @@
         <v>5465</v>
       </c>
       <c r="C295" s="120">
-        <v>5190</v>
+        <v>5394</v>
       </c>
       <c r="D295" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="296" spans="2:4" x14ac:dyDescent="0.2">
@@ -53477,10 +53914,10 @@
         <v>5465</v>
       </c>
       <c r="C296" s="120">
-        <v>5357</v>
+        <v>5371</v>
       </c>
       <c r="D296" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="297" spans="2:4" x14ac:dyDescent="0.2">
@@ -53488,7 +53925,7 @@
         <v>5465</v>
       </c>
       <c r="C297" s="120">
-        <v>5378</v>
+        <v>5365</v>
       </c>
       <c r="D297" s="120" t="s">
         <v>737</v>
@@ -53499,10 +53936,10 @@
         <v>5465</v>
       </c>
       <c r="C298" s="120">
-        <v>5307</v>
+        <v>5347</v>
       </c>
       <c r="D298" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="299" spans="2:4" x14ac:dyDescent="0.2">
@@ -53510,7 +53947,7 @@
         <v>5465</v>
       </c>
       <c r="C299" s="120">
-        <v>5345</v>
+        <v>5292</v>
       </c>
       <c r="D299" s="120" t="s">
         <v>737</v>
@@ -53521,10 +53958,10 @@
         <v>5465</v>
       </c>
       <c r="C300" s="120">
-        <v>5394</v>
+        <v>5343</v>
       </c>
       <c r="D300" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="301" spans="2:4" x14ac:dyDescent="0.2">
@@ -53532,10 +53969,10 @@
         <v>5465</v>
       </c>
       <c r="C301" s="120">
-        <v>5371</v>
+        <v>5374</v>
       </c>
       <c r="D301" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="302" spans="2:4" x14ac:dyDescent="0.2">
@@ -53543,10 +53980,10 @@
         <v>5465</v>
       </c>
       <c r="C302" s="120">
-        <v>5365</v>
+        <v>5390</v>
       </c>
       <c r="D302" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="303" spans="2:4" x14ac:dyDescent="0.2">
@@ -53554,7 +53991,7 @@
         <v>5465</v>
       </c>
       <c r="C303" s="120">
-        <v>5347</v>
+        <v>5341</v>
       </c>
       <c r="D303" s="120" t="s">
         <v>1032</v>
@@ -53565,365 +54002,365 @@
         <v>5465</v>
       </c>
       <c r="C304" s="120">
-        <v>5292</v>
+        <v>5336</v>
       </c>
       <c r="D304" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="305" spans="2:4" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B305" s="121">
         <v>5465</v>
       </c>
       <c r="C305" s="120">
-        <v>5343</v>
+        <v>5356</v>
       </c>
       <c r="D305" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="306" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B306" s="121">
         <v>5465</v>
       </c>
       <c r="C306" s="120">
-        <v>5374</v>
+        <v>5372</v>
       </c>
       <c r="D306" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="307" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B307" s="121">
         <v>5465</v>
       </c>
       <c r="C307" s="120">
-        <v>5350</v>
+        <v>5325</v>
       </c>
       <c r="D307" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="308" spans="2:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B308" s="121">
         <v>5465</v>
       </c>
       <c r="C308" s="120">
-        <v>5390</v>
+        <v>5397</v>
       </c>
       <c r="D308" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="309" spans="2:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B309" s="121">
         <v>5465</v>
       </c>
       <c r="C309" s="120">
-        <v>5341</v>
+        <v>5355</v>
       </c>
       <c r="D309" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="310" spans="2:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B310" s="121">
         <v>5465</v>
       </c>
       <c r="C310" s="120">
-        <v>5336</v>
+        <v>5377</v>
       </c>
       <c r="D310" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="311" spans="2:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B311" s="121">
         <v>5465</v>
       </c>
       <c r="C311" s="120">
-        <v>5356</v>
+        <v>5392</v>
       </c>
       <c r="D311" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="312" spans="2:4" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B312" s="121">
         <v>5465</v>
       </c>
       <c r="C312" s="120">
-        <v>5372</v>
+        <v>5375</v>
       </c>
       <c r="D312" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="313" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B313" s="121">
         <v>5465</v>
       </c>
       <c r="C313" s="120">
-        <v>5325</v>
+        <v>5354</v>
       </c>
       <c r="D313" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="314" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B314" s="121">
+    <row r="314" spans="1:4" s="136" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B314" s="137">
         <v>5465</v>
       </c>
-      <c r="C314" s="120">
-        <v>5397</v>
-      </c>
-      <c r="D314" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="315" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B315" s="121">
+      <c r="C314" s="136">
+        <v>5359</v>
+      </c>
+      <c r="D314" s="136" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A315" s="120" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B315" s="120">
         <v>5465</v>
       </c>
       <c r="C315" s="120">
-        <v>5355</v>
+        <v>5406</v>
       </c>
       <c r="D315" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="316" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B316" s="121">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B316" s="120">
         <v>5465</v>
       </c>
       <c r="C316" s="120">
-        <v>5377</v>
+        <v>5400</v>
       </c>
       <c r="D316" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="317" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B317" s="121">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B317" s="120">
         <v>5465</v>
       </c>
       <c r="C317" s="120">
-        <v>5392</v>
+        <v>5404</v>
       </c>
       <c r="D317" s="120" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="318" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B318" s="121">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B318" s="120">
         <v>5465</v>
       </c>
       <c r="C318" s="120">
-        <v>5375</v>
+        <v>5407</v>
       </c>
       <c r="D318" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="319" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B319" s="121">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B319" s="120">
         <v>5465</v>
       </c>
       <c r="C319" s="120">
-        <v>5354</v>
+        <v>5405</v>
       </c>
       <c r="D319" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="320" spans="2:4" s="136" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B320" s="137">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B320" s="120">
         <v>5465</v>
       </c>
-      <c r="C320" s="136">
-        <v>5359</v>
-      </c>
-      <c r="D320" s="136" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A321" s="120" t="s">
-        <v>2116</v>
-      </c>
+      <c r="C320" s="120">
+        <v>5402</v>
+      </c>
+      <c r="D320" s="120" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B321" s="120">
         <v>5465</v>
       </c>
       <c r="C321" s="120">
-        <v>5406</v>
+        <v>5403</v>
       </c>
       <c r="D321" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B322" s="120">
         <v>5465</v>
       </c>
       <c r="C322" s="120">
-        <v>5400</v>
+        <v>5401</v>
       </c>
       <c r="D322" s="120" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B323" s="120">
         <v>5465</v>
       </c>
       <c r="C323" s="120">
-        <v>5404</v>
+        <v>5455</v>
       </c>
       <c r="D323" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B324" s="120">
         <v>5465</v>
       </c>
       <c r="C324" s="120">
-        <v>5407</v>
+        <v>5420</v>
       </c>
       <c r="D324" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="325" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B325" s="120">
         <v>5465</v>
       </c>
       <c r="C325" s="120">
-        <v>5405</v>
+        <v>5444</v>
       </c>
       <c r="D325" s="120" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="326" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B326" s="120">
         <v>5465</v>
       </c>
       <c r="C326" s="120">
-        <v>5402</v>
+        <v>5454</v>
       </c>
       <c r="D326" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B327" s="120">
         <v>5465</v>
       </c>
       <c r="C327" s="120">
-        <v>5403</v>
+        <v>5424</v>
       </c>
       <c r="D327" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B328" s="120">
         <v>5465</v>
       </c>
       <c r="C328" s="120">
-        <v>5401</v>
+        <v>5412</v>
       </c>
       <c r="D328" s="120" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B329" s="120">
         <v>5465</v>
       </c>
       <c r="C329" s="120">
-        <v>5455</v>
+        <v>5423</v>
       </c>
       <c r="D329" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B330" s="120">
         <v>5465</v>
       </c>
       <c r="C330" s="120">
-        <v>5420</v>
+        <v>5445</v>
       </c>
       <c r="D330" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B331" s="120">
         <v>5465</v>
       </c>
       <c r="C331" s="120">
-        <v>5444</v>
+        <v>5437</v>
       </c>
       <c r="D331" s="120" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="332" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B332" s="120">
         <v>5465</v>
       </c>
       <c r="C332" s="120">
-        <v>5454</v>
+        <v>5425</v>
       </c>
       <c r="D332" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B333" s="120">
         <v>5465</v>
       </c>
       <c r="C333" s="120">
-        <v>5424</v>
+        <v>5421</v>
       </c>
       <c r="D333" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B334" s="120">
         <v>5465</v>
       </c>
       <c r="C334" s="120">
-        <v>5412</v>
+        <v>5415</v>
       </c>
       <c r="D334" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B335" s="120">
         <v>5465</v>
       </c>
       <c r="C335" s="120">
-        <v>5423</v>
+        <v>5456</v>
       </c>
       <c r="D335" s="120" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B336" s="120">
         <v>5465</v>
       </c>
       <c r="C336" s="120">
-        <v>5445</v>
+        <v>5413</v>
       </c>
       <c r="D336" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="337" spans="2:4" x14ac:dyDescent="0.2">
@@ -53931,7 +54368,7 @@
         <v>5465</v>
       </c>
       <c r="C337" s="120">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="D337" s="120" t="s">
         <v>1032</v>
@@ -53942,10 +54379,10 @@
         <v>5465</v>
       </c>
       <c r="C338" s="120">
-        <v>5425</v>
+        <v>5422</v>
       </c>
       <c r="D338" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="339" spans="2:4" x14ac:dyDescent="0.2">
@@ -53953,10 +54390,10 @@
         <v>5465</v>
       </c>
       <c r="C339" s="120">
-        <v>5421</v>
+        <v>5414</v>
       </c>
       <c r="D339" s="120" t="s">
-        <v>1032</v>
+        <v>737</v>
       </c>
     </row>
     <row r="340" spans="2:4" x14ac:dyDescent="0.2">
@@ -53964,10 +54401,10 @@
         <v>5465</v>
       </c>
       <c r="C340" s="120">
-        <v>5415</v>
+        <v>5439</v>
       </c>
       <c r="D340" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="341" spans="2:4" x14ac:dyDescent="0.2">
@@ -53975,10 +54412,10 @@
         <v>5465</v>
       </c>
       <c r="C341" s="120">
-        <v>5456</v>
+        <v>5432</v>
       </c>
       <c r="D341" s="120" t="s">
-        <v>737</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="342" spans="2:4" x14ac:dyDescent="0.2">
@@ -53986,7 +54423,7 @@
         <v>5465</v>
       </c>
       <c r="C342" s="120">
-        <v>5413</v>
+        <v>5433</v>
       </c>
       <c r="D342" s="120" t="s">
         <v>1032</v>
@@ -53997,86 +54434,20 @@
         <v>5465</v>
       </c>
       <c r="C343" s="120">
-        <v>5438</v>
+        <v>5457</v>
       </c>
       <c r="D343" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="344" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B344" s="120">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4" s="136" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B344" s="136">
         <v>5465</v>
       </c>
-      <c r="C344" s="120">
-        <v>5422</v>
-      </c>
-      <c r="D344" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="345" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B345" s="120">
-        <v>5465</v>
-      </c>
-      <c r="C345" s="120">
-        <v>5414</v>
-      </c>
-      <c r="D345" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="346" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B346" s="120">
-        <v>5465</v>
-      </c>
-      <c r="C346" s="120">
-        <v>5439</v>
-      </c>
-      <c r="D346" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="347" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B347" s="120">
-        <v>5465</v>
-      </c>
-      <c r="C347" s="120">
-        <v>5432</v>
-      </c>
-      <c r="D347" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="348" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B348" s="120">
-        <v>5465</v>
-      </c>
-      <c r="C348" s="120">
-        <v>5433</v>
-      </c>
-      <c r="D348" s="120" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="349" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B349" s="120">
-        <v>5465</v>
-      </c>
-      <c r="C349" s="120">
-        <v>5457</v>
-      </c>
-      <c r="D349" s="120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="350" spans="2:4" s="136" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B350" s="136">
-        <v>5465</v>
-      </c>
-      <c r="C350" s="136">
+      <c r="C344" s="136">
         <v>5434</v>
       </c>
-      <c r="D350" s="136" t="s">
+      <c r="D344" s="136" t="s">
         <v>737</v>
       </c>
     </row>
